--- a/datos/licitaciones_en_plazo.xlsx
+++ b/datos/licitaciones_en_plazo.xlsx
@@ -768,11 +768,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="n"/>
       <c r="B2" s="3" t="n">
         <v>46310.79166666666</v>
       </c>
@@ -870,11 +866,7 @@
       <c r="Y2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="n"/>
       <c r="B3" s="3" t="n">
         <v>46310.99930555555</v>
       </c>
@@ -968,11 +960,7 @@
       <c r="Y3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="n"/>
       <c r="B4" s="3" t="n">
         <v>46311.54166666666</v>
       </c>
@@ -1062,11 +1050,7 @@
       <c r="Y4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="n"/>
       <c r="B5" s="3" t="n">
         <v>46314.54166666666</v>
       </c>
@@ -1152,11 +1136,7 @@
       <c r="Y5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="n"/>
       <c r="B6" s="3" t="n">
         <v>46314.99930555555</v>
       </c>
@@ -1250,11 +1230,7 @@
       <c r="Y6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="n"/>
       <c r="B7" s="3" t="n">
         <v>46316.99930555555</v>
       </c>
@@ -1348,11 +1324,7 @@
       <c r="Y7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="n"/>
       <c r="B8" s="3" t="n">
         <v>46317.99930555555</v>
       </c>
@@ -1446,11 +1418,7 @@
       <c r="Y8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="n"/>
       <c r="B9" s="3" t="n">
         <v>46317.99930555555</v>
       </c>
@@ -1540,11 +1508,7 @@
       <c r="Y9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="n"/>
       <c r="B10" s="3" t="n">
         <v>46318.99930555555</v>
       </c>
@@ -1642,11 +1606,7 @@
       <c r="Y10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="n"/>
       <c r="B11" s="3" t="n">
         <v>46321.375</v>
       </c>
@@ -1740,11 +1700,7 @@
       <c r="Y11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="n"/>
       <c r="B12" s="3" t="n">
         <v>46321.54166666666</v>
       </c>
@@ -1834,11 +1790,7 @@
       <c r="Y12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="n"/>
       <c r="B13" s="3" t="n">
         <v>46321.79166666666</v>
       </c>
@@ -1928,11 +1880,7 @@
       <c r="Y13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="n"/>
       <c r="B14" s="3" t="n">
         <v>46321.99930555555</v>
       </c>
@@ -2026,11 +1974,7 @@
       <c r="Y14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="n"/>
       <c r="B15" s="3" t="n">
         <v>46321.99930555555</v>
       </c>
@@ -2124,11 +2068,7 @@
       <c r="Y15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="n"/>
       <c r="B16" s="3" t="n">
         <v>46322.99930555555</v>
       </c>
@@ -2222,11 +2162,7 @@
       <c r="Y16" s="2" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="n"/>
       <c r="B17" s="3" t="n">
         <v>46322.99930555555</v>
       </c>
@@ -2320,11 +2256,7 @@
       <c r="Y17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="n"/>
       <c r="B18" s="3" t="n">
         <v>46323.04097222222</v>
       </c>
@@ -2422,11 +2354,7 @@
       <c r="Y18" s="2" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="n"/>
       <c r="B19" s="3" t="n">
         <v>46323.5</v>
       </c>
@@ -2516,11 +2444,7 @@
       <c r="Y19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
       <c r="B20" s="3" t="n">
         <v>46323.5</v>
       </c>
@@ -2610,11 +2534,7 @@
       <c r="Y20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="n"/>
       <c r="B21" s="3" t="n">
         <v>46323.5</v>
       </c>
@@ -2700,11 +2620,7 @@
       <c r="Y21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="n"/>
       <c r="B22" s="3" t="n">
         <v>46323.99930555555</v>
       </c>
@@ -2794,11 +2710,7 @@
       <c r="Y22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="n"/>
       <c r="B23" s="3" t="n">
         <v>46323.99930555555</v>
       </c>
@@ -2896,11 +2808,7 @@
       <c r="Y23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="n"/>
       <c r="B24" s="3" t="n">
         <v>46323.99930555555</v>
       </c>
@@ -2994,11 +2902,7 @@
       <c r="Y24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="n"/>
       <c r="B25" s="3" t="n">
         <v>46323.99930555555</v>
       </c>
@@ -3092,11 +2996,7 @@
       <c r="Y25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="n"/>
       <c r="B26" s="3" t="n">
         <v>46324.58333333334</v>
       </c>
@@ -3186,11 +3086,7 @@
       <c r="Y26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="n"/>
       <c r="B27" s="3" t="n">
         <v>46324.99930555555</v>
       </c>
@@ -3288,11 +3184,7 @@
       <c r="Y27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="n"/>
       <c r="B28" s="3" t="n">
         <v>46324.99930555555</v>
       </c>
@@ -3394,11 +3286,7 @@
       <c r="Y28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="n"/>
       <c r="B29" s="3" t="n">
         <v>46324.99930555555</v>
       </c>
@@ -3488,11 +3376,7 @@
       <c r="Y29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="n"/>
       <c r="B30" s="3" t="n">
         <v>46325.58333333334</v>
       </c>
@@ -3582,11 +3466,7 @@
       <c r="Y30" s="2" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="n"/>
       <c r="B31" s="3" t="n">
         <v>46328.33333333334</v>
       </c>
@@ -3684,11 +3564,7 @@
       <c r="Y31" s="2" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
       <c r="B32" s="3" t="n">
         <v>46328.58333333334</v>
       </c>
@@ -3782,11 +3658,7 @@
       <c r="Y32" s="2" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="n"/>
       <c r="B33" s="3" t="n">
         <v>46328.58333333334</v>
       </c>
@@ -3880,11 +3752,7 @@
       <c r="Y33" s="2" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="n"/>
       <c r="B34" s="3" t="n">
         <v>46328.99930555555</v>
       </c>
@@ -3978,11 +3846,7 @@
       <c r="Y34" s="2" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="n"/>
       <c r="B35" s="3" t="n">
         <v>46329.58333333334</v>
       </c>
@@ -4080,11 +3944,7 @@
       <c r="Y35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
       <c r="B36" s="3" t="n">
         <v>46329.79166666666</v>
       </c>
@@ -4178,11 +4038,7 @@
       <c r="Y36" s="2" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="n"/>
       <c r="B37" s="3" t="n">
         <v>46329.79166666666</v>
       </c>
@@ -4276,11 +4132,7 @@
       <c r="Y37" s="2" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="n"/>
       <c r="B38" s="3" t="n">
         <v>46329.79166666666</v>
       </c>
@@ -4374,11 +4226,7 @@
       <c r="Y38" s="2" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="n"/>
       <c r="B39" s="3" t="n">
         <v>46329.99930555555</v>
       </c>
@@ -4468,11 +4316,7 @@
       <c r="Y39" s="2" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="n"/>
       <c r="B40" s="3" t="n">
         <v>46329.99930555555</v>
       </c>
@@ -4562,11 +4406,7 @@
       <c r="Y40" s="2" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="n"/>
       <c r="B41" s="3" t="n">
         <v>46329.99930555555</v>
       </c>
@@ -4660,11 +4500,7 @@
       <c r="Y41" s="2" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="n"/>
       <c r="B42" s="3" t="n">
         <v>46329.99930555555</v>
       </c>
@@ -4754,11 +4590,7 @@
       <c r="Y42" s="2" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
       <c r="B43" s="3" t="n">
         <v>46331.99930555555</v>
       </c>
@@ -4848,11 +4680,7 @@
       <c r="Y43" s="2" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="n"/>
       <c r="B44" s="3" t="n">
         <v>46332.99930555555</v>
       </c>
@@ -4942,11 +4770,7 @@
       <c r="Y44" s="2" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="n"/>
       <c r="B45" s="3" t="n">
         <v>46335.99930555555</v>
       </c>
@@ -5040,11 +4864,7 @@
       <c r="Y45" s="2" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="n"/>
       <c r="B46" s="3" t="n">
         <v>46335.99930555555</v>
       </c>
@@ -5146,11 +4966,7 @@
       <c r="Y46" s="2" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="n"/>
       <c r="B47" s="3" t="n">
         <v>46335.99930555555</v>
       </c>
@@ -5248,11 +5064,7 @@
       <c r="Y47" s="2" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="n"/>
       <c r="B48" s="3" t="n">
         <v>46335.99930555555</v>
       </c>
@@ -5342,11 +5154,7 @@
       <c r="Y48" s="2" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="n"/>
       <c r="B49" s="3" t="n">
         <v>46350.45833333334</v>
       </c>
@@ -5440,11 +5248,7 @@
       <c r="Y49" s="2" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>SÍ</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="n"/>
       <c r="B50" s="3" t="n">
         <v>48099.58333333334</v>
       </c>
@@ -5738,7 +5542,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46310.33159722222</v>
+        <v>46310.49417824074</v>
       </c>
     </row>
     <row r="4">
@@ -5773,7 +5577,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>0 fichero(s) mensual(es) + 30 página(s) del feed</t>
+          <t>0 fichero(s) mensual(es) + 7 página(s) del feed</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5588,7 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>14701</v>
+        <v>3226</v>
       </c>
     </row>
     <row r="8">
@@ -5795,7 +5599,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>06/10/2026 – 14/10/2026</t>
+          <t>13/10/2026 – 14/10/2026</t>
         </is>
       </c>
     </row>

--- a/datos/licitaciones_en_plazo.xlsx
+++ b/datos/licitaciones_en_plazo.xlsx
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46310.49417824074</v>
+        <v>46310.50722222222</v>
       </c>
     </row>
     <row r="4">

--- a/datos/licitaciones_en_plazo.xlsx
+++ b/datos/licitaciones_en_plazo.xlsx
@@ -258,8 +258,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EnPlazo" displayName="EnPlazo" ref="A1:Y50" headerRowCount="1">
-  <autoFilter ref="A1:Y50"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EnPlazo" displayName="EnPlazo" ref="A1:Y55" headerRowCount="1">
+  <autoFilter ref="A1:Y55"/>
   <tableColumns count="25">
     <tableColumn id="1" name="Nueva"/>
     <tableColumn id="2" name="Fecha límite"/>
@@ -610,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Y50"/>
+  <dimension ref="A1:Y55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1052,38 +1052,46 @@
     <row r="5">
       <c r="A5" s="2" t="n"/>
       <c r="B5" s="3" t="n">
-        <v>46314.54166666666</v>
+        <v>46311.75</v>
       </c>
       <c r="C5" s="4">
         <f>IF(B5="","",INT(B5)-TODAY())</f>
         <v/>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3230429.22</v>
+        <v>20042739.4</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3230429.22</v>
+        <v>20042739.4</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Andalucía</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>ADIF - Presidencia</t>
+          <t>Presidencia de la Autoridad Portuaria de Almería</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Ejecución de las obras correspondientes a los proyectos de reposición y ejecución de cerramientos en el ámbito de la red convencional. Línea 400 (p.k. 16/717 al 24/380, 17/732 al 24/318, 121/210 al 122/140, 122/140 al 123/200, 142/800 al 144/550), línea 406 (p.k. 1/322 al 1/384, 131/848 al 132/215), línea 440 (p.k. 95/630 al 96/450) y línea 444 (p.k.3/170 al 9/940).</t>
+          <t>Actuaciones en el frente litoral en espacios Puerto-Ciudad de Almería</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3.26/27507.0212</t>
+          <t>15/O/A/AL26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -1092,19 +1100,19 @@
         </is>
       </c>
       <c r="M5" s="6" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>D5-5</t>
+          <t>G6-5</t>
         </is>
       </c>
       <c r="O5" s="7" t="n">
-        <v>0.49</v>
+        <v>0.45</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Cuantificable mediante fórmula (Compromiso de utilización CDE Adif) 2 | Evaluable mediante juicio de valor 49 (JV) | Precio 49</t>
+          <t>Cuantitativos 55 | Cualitativos 45 (JV)</t>
         </is>
       </c>
       <c r="Q5" s="2" t="n"/>
@@ -1112,7 +1120,7 @@
       <c r="S5" s="4" t="n"/>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45234100</t>
+          <t>45233140; 45262311; 71351810; 45233200; 45211360; 45231400; 45231300; 45223810</t>
         </is>
       </c>
       <c r="U5" s="8" t="inlineStr">
@@ -1138,46 +1146,38 @@
     <row r="6">
       <c r="A6" s="2" t="n"/>
       <c r="B6" s="3" t="n">
-        <v>46314.99930555555</v>
+        <v>46314.54166666666</v>
       </c>
       <c r="C6" s="4">
         <f>IF(B6="","",INT(B6)-TODAY())</f>
         <v/>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2207320.13</v>
+        <v>3230429.22</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2207320.13</v>
+        <v>3230429.22</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Departamento de Salud Valencia - Arnau de Vilanova - Llíria. Dirección Económica-Gerencia</t>
+          <t>ADIF - Presidencia</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Obras de Reforma de Climatización Fase II del Hospital Arnau de Vilanova del Departamento de Salud De Valencia-Arnau de Vilanova-Llíria</t>
+          <t>Ejecución de las obras correspondientes a los proyectos de reposición y ejecución de cerramientos en el ámbito de la red convencional. Línea 400 (p.k. 16/717 al 24/380, 17/732 al 24/318, 121/210 al 122/140, 122/140 al 123/200, 142/800 al 144/550), línea 406 (p.k. 1/322 al 1/384, 131/848 al 132/215), línea 440 (p.k. 95/630 al 96/450) y línea 444 (p.k.3/170 al 9/940).</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1564/2026</t>
+          <t>3.26/27507.0212</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1186,27 +1186,27 @@
         </is>
       </c>
       <c r="M6" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="N6" s="2" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>D5-5</t>
+        </is>
+      </c>
       <c r="O6" s="7" t="n">
-        <v>0.36</v>
+        <v>0.49</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10- Precio 45 | 8- Ampliación plazo garantía 9 | 9-Incremento dedicación en obra del jefe de obra 10 | 1-Criterios cualitativos-juicio de valor 36 (JV)</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>complementaria 3%; definitiva 5%</t>
-        </is>
-      </c>
+          <t>Cuantificable mediante fórmula (Compromiso de utilización CDE Adif) 2 | Evaluable mediante juicio de valor 49 (JV) | Precio 49</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="4" t="n"/>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45215140; 45331000; 45262900; 45310000</t>
+          <t>45234100</t>
         </is>
       </c>
       <c r="U6" s="8" t="inlineStr">
@@ -1232,75 +1232,75 @@
     <row r="7">
       <c r="A7" s="2" t="n"/>
       <c r="B7" s="3" t="n">
-        <v>46316.99930555555</v>
+        <v>46314.99930555555</v>
       </c>
       <c r="C7" s="4">
         <f>IF(B7="","",INT(B7)-TODAY())</f>
         <v/>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1556552.43</v>
+        <v>2207320.13</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1556552.43</v>
+        <v>2207320.13</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Brenes (Sevilla)</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Pleno del Ayuntamiento de Brenes</t>
+          <t>Departamento de Salud Valencia - Arnau de Vilanova - Llíria. Dirección Económica-Gerencia</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Obras contempladas en el proyecto de Teatro Municipal (Adecuación de salón de usos múltiples a teatro)</t>
+          <t>Obras de Reforma de Climatización Fase II del Hospital Arnau de Vilanova del Departamento de Salud De Valencia-Arnau de Vilanova-Llíria</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3206/2026</t>
+          <t>1564/2026</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Abierto simplificado</t>
+          <t>Abierto</t>
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="7" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Mejora: Suministro escenario modular 10 | Mejora: Plantación olivo 10 | Precio a la baja 65 | Mejora: Reducción plazo de ejecución 15</t>
+          <t>10- Precio 45 | 8- Ampliación plazo garantía 9 | 9-Incremento dedicación en obra del jefe de obra 10 | 1-Criterios cualitativos-juicio de valor 36 (JV)</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>definitiva 5%</t>
+          <t>complementaria 3%; definitiva 5%</t>
         </is>
       </c>
       <c r="R7" s="2" t="n"/>
       <c r="S7" s="4" t="n"/>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45212322; 45212300; 45454000</t>
+          <t>45215140; 45331000; 45262900; 45310000</t>
         </is>
       </c>
       <c r="U7" s="8" t="inlineStr">
@@ -1326,42 +1326,46 @@
     <row r="8">
       <c r="A8" s="2" t="n"/>
       <c r="B8" s="3" t="n">
-        <v>46317.99930555555</v>
+        <v>46316.54166666666</v>
       </c>
       <c r="C8" s="4">
         <f>IF(B8="","",INT(B8)-TODAY())</f>
         <v/>
       </c>
       <c r="D8" s="5" t="n">
-        <v>700330.77</v>
+        <v>38364304.82</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>700330.77</v>
+        <v>46037165.78</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n"/>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno Local del Ayuntamiento de Hornachuelos</t>
+          <t>Consejo de Administración de la Autoridad Portuaria de Valencia</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Contratación de la obra relativa al proyecto de construcción de pabellón polivalente para actividades relacionadas con el desarrollo económico en el recinto ferial Las Erillas (zona norte) de Hornachuelos (Córdoba)</t>
+          <t>Adaptación del espigón del Turia para mejora del área de pasaje en el Puerto de Valencia</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10893/2026</t>
+          <t>EC26-C02-01510</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1370,31 +1374,31 @@
         </is>
       </c>
       <c r="M8" s="6" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>C4-2</t>
+          <t>F7-6; F5-5; F1-5</t>
         </is>
       </c>
       <c r="O8" s="7" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>REDUCCION DEL PLAZO DE EJECUCION 40 | MEJORA MÓDULO 40 | OFERTA ECONÓMICA 20</t>
+          <t>Criterios evaluables mediante juicio de valor 49 (JV) | Oferta económica 51</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>definitiva 5%</t>
+          <t>definitiva 5%; complementaria 5%</t>
         </is>
       </c>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="4" t="n"/>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>45212000</t>
+          <t>45241100</t>
         </is>
       </c>
       <c r="U8" s="8" t="inlineStr">
@@ -1402,11 +1406,7 @@
           <t>PCAP</t>
         </is>
       </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>PPT</t>
-        </is>
-      </c>
+      <c r="V8" s="2" t="n"/>
       <c r="W8" s="8" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -1420,17 +1420,17 @@
     <row r="9">
       <c r="A9" s="2" t="n"/>
       <c r="B9" s="3" t="n">
-        <v>46317.99930555555</v>
+        <v>46316.58333333334</v>
       </c>
       <c r="C9" s="4">
         <f>IF(B9="","",INT(B9)-TODAY())</f>
         <v/>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1090919.91</v>
+        <v>15000000</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1309103.09</v>
+        <v>15000000</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1439,52 +1439,56 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno Local del Ayuntamiento de El Ejido</t>
+          <t>Empresa de Transformación Agraria S.A.,S.M.E., M.P., (TRAGSA)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Es objeto de la presente licitación es la contratación de la ejecución del proyecto de obras denominado: Proyecto de construcción de adecuación del complejo deportivo en el núcleo de Almerimar. Fase III, conforme a las especificaciones y características expuestas en el presente pliego y en el proyecto técnico.</t>
+          <t>Conclusión del Acuerdo Marco para Alquiler de Maquinaria de Obra Civil, Agrícola y Forestal, y Camiones, dotada de operario, para Las Actuaciones de La Gerencia Provincial de Tragsa en Córdoba, incluidas obras Financiadas con Fondos Europeos</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2026 1160</t>
+          <t>TSA0084239</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>Abierto simplificado</t>
+          <t>Abierto</t>
         </is>
       </c>
       <c r="M9" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="N9" s="2" t="n"/>
+        <v>24</v>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>C*-1; A*-1; K*-1; E*-1; D*-1; G*-1</t>
+        </is>
+      </c>
       <c r="O9" s="7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Criterios evaluables mediante un juicio de valor 25 (JV) | Proposición económica 75</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>definitiva 5%</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="n"/>
+          <t>Precio de la oferta 100</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="S9" s="4" t="n"/>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>45200000</t>
+          <t>45500000</t>
         </is>
       </c>
       <c r="U9" s="8" t="inlineStr">
@@ -1510,79 +1514,75 @@
     <row r="10">
       <c r="A10" s="2" t="n"/>
       <c r="B10" s="3" t="n">
-        <v>46318.99930555555</v>
+        <v>46316.99930555555</v>
       </c>
       <c r="C10" s="4">
         <f>IF(B10="","",INT(B10)-TODAY())</f>
         <v/>
       </c>
       <c r="D10" s="5" t="n">
-        <v>3018964.07</v>
+        <v>1556552.43</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3924653.29</v>
+        <v>1556552.43</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Alicante</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>ELCHE</t>
+          <t>Brenes (Sevilla)</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Departamento de Salud de Elche. Dirección Económica-Gerencia</t>
+          <t>Pleno del Ayuntamiento de Brenes</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Obras de reforma integral de la Unidad de Cuidados Intensivos (Uci) del Hospital General Universitario de Elche</t>
+          <t>Obras contempladas en el proyecto de Teatro Municipal (Adecuación de salón de usos múltiples a teatro)</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>PA 428/2026</t>
+          <t>3206/2026</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Abierto simplificado</t>
         </is>
       </c>
       <c r="M10" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>J2-4</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N10" s="2" t="n"/>
       <c r="O10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>OFERTA ECONOMICA 0 | CRITERIOS CUALITATIVOS DE CARÁCTER AUTOMÁTICO 10 | CRITERIOS QUE DEPENDE DE UN JUICIO DE VALOR 0 (JV)</t>
+          <t>Mejora: Suministro escenario modular 10 | Mejora: Plantación olivo 10 | Precio a la baja 65 | Mejora: Reducción plazo de ejecución 15</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>definitiva 5%; complementaria 5%</t>
+          <t>definitiva 5%</t>
         </is>
       </c>
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="4" t="n"/>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45215140; 45215142</t>
+          <t>45212322; 45212300; 45454000</t>
         </is>
       </c>
       <c r="U10" s="8" t="inlineStr">
@@ -1608,75 +1608,75 @@
     <row r="11">
       <c r="A11" s="2" t="n"/>
       <c r="B11" s="3" t="n">
-        <v>46321.375</v>
+        <v>46317.99930555555</v>
       </c>
       <c r="C11" s="4">
         <f>IF(B11="","",INT(B11)-TODAY())</f>
         <v/>
       </c>
       <c r="D11" s="5" t="n">
-        <v>889866.1</v>
+        <v>700330.77</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1067839.32</v>
+        <v>700330.77</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Alicante</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Alicante</t>
-        </is>
-      </c>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Mercados Centrales De Abastecimiento de Alicante S.A.</t>
+          <t>Junta de Gobierno Local del Ayuntamiento de Hornachuelos</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Sustitución de las cubiertas de fibrocemento de la nave III de Mercalicante</t>
+          <t>Contratación de la obra relativa al proyecto de construcción de pabellón polivalente para actividades relacionadas con el desarrollo económico en el recinto ferial Las Erillas (zona norte) de Hornachuelos (Córdoba)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21/2026EXPL</t>
+          <t>10893/2026</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Abierto simplificado</t>
+          <t>Abierto</t>
         </is>
       </c>
       <c r="M11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N11" s="2" t="n"/>
+        <v>7</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>C4-2</t>
+        </is>
+      </c>
       <c r="O11" s="7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Plan de obra 5 (JV) | Experiencia del jefe y del encargado de obra 10 | Ampliación del plazo de garantía 5 | Memoria y estudio de obra 20 (JV) | Oferta económica 54 | Mantenimiento de la cubierta y líneas de vida 6</t>
+          <t>REDUCCION DEL PLAZO DE EJECUCION 40 | MEJORA MÓDULO 40 | OFERTA ECONÓMICA 20</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>complementaria 5%; definitiva 5%</t>
+          <t>definitiva 5%</t>
         </is>
       </c>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="4" t="n"/>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45000000; 45421160; 45261220; 45262660; 45261420</t>
+          <t>45212000</t>
         </is>
       </c>
       <c r="U11" s="8" t="inlineStr">
@@ -1702,17 +1702,17 @@
     <row r="12">
       <c r="A12" s="2" t="n"/>
       <c r="B12" s="3" t="n">
-        <v>46321.54166666666</v>
+        <v>46317.99930555555</v>
       </c>
       <c r="C12" s="4">
         <f>IF(B12="","",INT(B12)-TODAY())</f>
         <v/>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3837538.71</v>
+        <v>1090919.91</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4221292.58</v>
+        <v>1309103.09</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1721,52 +1721,52 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Gerencia de Sevilla Activa SAU</t>
+          <t>Junta de Gobierno Local del Ayuntamiento de El Ejido</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Terminación de 50 Viviendas Protegidas</t>
+          <t>Es objeto de la presente licitación es la contratación de la ejecución del proyecto de obras denominado: Proyecto de construcción de adecuación del complejo deportivo en el núcleo de Almerimar. Fase III, conforme a las especificaciones y características expuestas en el presente pliego y en el proyecto técnico.</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>A41420191-2026/000082-PaA</t>
+          <t>2026 1160</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Abierto simplificado</t>
         </is>
       </c>
       <c r="M12" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>C*-5; G*-5; G6-4; C4-4</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="N12" s="2" t="n"/>
       <c r="O12" s="7" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>memoria técnica [1] 30 (JV) | ampliación del plazo de garantía de la obra sobre el mínimo de un año [3] 15 | visita guiada [2] 15 | Aspecto Económico (precio) [1] 40</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="n"/>
+          <t>Criterios evaluables mediante un juicio de valor 25 (JV) | Proposición económica 75</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>definitiva 5%</t>
+        </is>
+      </c>
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="4" t="n"/>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>45211000</t>
+          <t>45200000</t>
         </is>
       </c>
       <c r="U12" s="8" t="inlineStr">
@@ -1792,71 +1792,79 @@
     <row r="13">
       <c r="A13" s="2" t="n"/>
       <c r="B13" s="3" t="n">
-        <v>46321.79166666666</v>
+        <v>46318.99930555555</v>
       </c>
       <c r="C13" s="4">
         <f>IF(B13="","",INT(B13)-TODAY())</f>
         <v/>
       </c>
       <c r="D13" s="5" t="n">
-        <v>1650495.98</v>
+        <v>3018964.07</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1650495.98</v>
+        <v>3924653.29</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Málaga</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n"/>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>ELCHE</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Instituto de Turismo de España (TURESPAÑA)</t>
+          <t>Departamento de Salud de Elche. Dirección Económica-Gerencia</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Contrato para la ejecución de obras de la Fase II de las obras para la protección y consolidación del frente de acantilado del parador de turismo de Nerja (Málaga)</t>
+          <t>Obras de reforma integral de la Unidad de Cuidados Intensivos (Uci) del Hospital General Universitario de Elche</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>020026C00098</t>
+          <t>PA 428/2026</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>Abierto simplificado</t>
+          <t>Abierto</t>
         </is>
       </c>
       <c r="M13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N13" s="2" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>J2-4</t>
+        </is>
+      </c>
       <c r="O13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>OFERTA ECONÓMICA 65 | OTROS CRITERIOS CUANTIFICABLES AUTOMATICAMENTE 35</t>
+          <t>OFERTA ECONOMICA 0 | CRITERIOS CUALITATIVOS DE CARÁCTER AUTOMÁTICO 10 | CRITERIOS QUE DEPENDE DE UN JUICIO DE VALOR 0 (JV)</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>complementaria 5%; definitiva 5%</t>
+          <t>definitiva 5%; complementaria 5%</t>
         </is>
       </c>
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="4" t="n"/>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45200000</t>
+          <t>45215140; 45215142</t>
         </is>
       </c>
       <c r="U13" s="8" t="inlineStr">
@@ -1882,42 +1890,46 @@
     <row r="14">
       <c r="A14" s="2" t="n"/>
       <c r="B14" s="3" t="n">
-        <v>46321.99930555555</v>
+        <v>46321.375</v>
       </c>
       <c r="C14" s="4">
         <f>IF(B14="","",INT(B14)-TODAY())</f>
         <v/>
       </c>
       <c r="D14" s="5" t="n">
-        <v>636363.64</v>
+        <v>889866.1</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>636363.64</v>
+        <v>1067839.32</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Huelva</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n"/>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Alicante</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno del Ayuntamiento de Almonte</t>
+          <t>Mercados Centrales De Abastecimiento de Alicante S.A.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>ejecución de obras del proyecto de ejecución para la rehabilitación energética del edificio "hacienda santa maría" -proyectos Miteco- derivadas de proyecto subvencionado por el ministerio para la transición ecológica y el reto demográfico en aplicación del Real decreto 842/2024, de 27 de agosto,</t>
+          <t>Sustitución de las cubiertas de fibrocemento de la nave III de Mercalicante</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12054/2026</t>
+          <t>21/2026EXPL</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1928,29 +1940,25 @@
       <c r="M14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>C*-3</t>
-        </is>
-      </c>
+      <c r="N14" s="2" t="n"/>
       <c r="O14" s="7" t="n">
         <v>0.25</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Procedencia de materiales y proveedores 4 (JV) | Compromiso de reducción del plazo de ejecución de la obra 25 | Recursos: personal, maquinaria y medios auxiliares 7 (JV) | Mejoras sociales de inserción 10 | Propuesta Plan de Obra 5 (JV) | Organización de los trabajos 5 (JV) | Ampliación de garantía 10 | Mejoras ambientales y/o de accesibilidad 20 | Propuesta del Plan de Aseguramiento de la Calidad 4 (JV) | Medidas medioambientales 10</t>
+          <t>Plan de obra 5 (JV) | Experiencia del jefe y del encargado de obra 10 | Ampliación del plazo de garantía 5 | Memoria y estudio de obra 20 (JV) | Oferta económica 54 | Mantenimiento de la cubierta y líneas de vida 6</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>definitiva 5%</t>
+          <t>complementaria 5%; definitiva 5%</t>
         </is>
       </c>
       <c r="R14" s="2" t="n"/>
       <c r="S14" s="4" t="n"/>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45200000</t>
+          <t>45000000; 45421160; 45261220; 45262660; 45261420</t>
         </is>
       </c>
       <c r="U14" s="8" t="inlineStr">
@@ -1976,17 +1984,17 @@
     <row r="15">
       <c r="A15" s="2" t="n"/>
       <c r="B15" s="3" t="n">
-        <v>46321.99930555555</v>
+        <v>46321.54166666666</v>
       </c>
       <c r="C15" s="4">
         <f>IF(B15="","",INT(B15)-TODAY())</f>
         <v/>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1025843.16</v>
+        <v>3837538.71</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1025843.16</v>
+        <v>4221292.58</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1995,56 +2003,52 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Málaga</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Alhaurín el Grande</t>
-        </is>
-      </c>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Alhaurín el Grande</t>
+          <t>Gerencia de Sevilla Activa SAU</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de obras de renaturalización de las Avenidas Blas Infante y Libertad. Tramo 4</t>
+          <t>Terminación de 50 Viviendas Protegidas</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25734/2026 BLAS INFANTE Y LIBERTAD</t>
+          <t>A41420191-2026/000082-PaA</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Abierto simplificado</t>
+          <t>Abierto</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="N15" s="2" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>C*-5; G*-5; G6-4; C4-4</t>
+        </is>
+      </c>
       <c r="O15" s="7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Proposición económica 80 | Memoria constructiva y programa de trabajo 4 (JV) | Medidas para reducir el impacto Ambiental 2 (JV) | Medidas para reducir el impacto urbano de la obra 4 (JV) | ampliación en el plazo de garantía 10</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>definitiva 5%</t>
-        </is>
-      </c>
+          <t>memoria técnica [1] 30 (JV) | ampliación del plazo de garantía de la obra sobre el mínimo de un año [3] 15 | visita guiada [2] 15 | Aspecto Económico (precio) [1] 40</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="n"/>
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="4" t="n"/>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>45223210; 45262520; 45233140; 45262210; 45112000; 45232100</t>
+          <t>45211000</t>
         </is>
       </c>
       <c r="U15" s="8" t="inlineStr">
@@ -2070,17 +2074,17 @@
     <row r="16">
       <c r="A16" s="2" t="n"/>
       <c r="B16" s="3" t="n">
-        <v>46322.99930555555</v>
+        <v>46321.79166666666</v>
       </c>
       <c r="C16" s="4">
         <f>IF(B16="","",INT(B16)-TODAY())</f>
         <v/>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1408264.46</v>
+        <v>1650495.98</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1408264.46</v>
+        <v>1650495.98</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -2089,23 +2093,23 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="H16" s="2" t="n"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno de la Diputación Provincial de Almería</t>
+          <t>Instituto de Turismo de España (TURESPAÑA)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Obras De Urbanización Para Un Complejo Deportivo. Vera 72PPOS24-27BI</t>
+          <t>Contrato para la ejecución de obras de la Fase II de las obras para la protección y consolidación del frente de acantilado del parador de turismo de Nerja (Málaga)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2026/D31000/006-013/00078</t>
+          <t>020026C00098</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2114,31 +2118,27 @@
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>G6-4</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="N16" s="2" t="n"/>
       <c r="O16" s="7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Oferta técnica 25 (JV) | Precio 75</t>
+          <t>OFERTA ECONÓMICA 65 | OTROS CRITERIOS CUANTIFICABLES AUTOMATICAMENTE 35</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>definitiva 5%; complementaria 5%</t>
+          <t>complementaria 5%; definitiva 5%</t>
         </is>
       </c>
       <c r="R16" s="2" t="n"/>
       <c r="S16" s="4" t="n"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45233200</t>
+          <t>45200000</t>
         </is>
       </c>
       <c r="U16" s="8" t="inlineStr">
@@ -2164,17 +2164,17 @@
     <row r="17">
       <c r="A17" s="2" t="n"/>
       <c r="B17" s="3" t="n">
-        <v>46322.99930555555</v>
+        <v>46321.99930555555</v>
       </c>
       <c r="C17" s="4">
         <f>IF(B17="","",INT(B17)-TODAY())</f>
         <v/>
       </c>
       <c r="D17" s="5" t="n">
-        <v>826446.28</v>
+        <v>636363.64</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>826446.28</v>
+        <v>636363.64</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -2183,23 +2183,23 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno de la Diputación Provincial de Almería</t>
+          <t>Junta de Gobierno del Ayuntamiento de Almonte</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Rehabilitación Y Mejora De Edificios Municipales. Benahadux 19PPOS24-27BII</t>
+          <t>ejecución de obras del proyecto de ejecución para la rehabilitación energética del edificio "hacienda santa maría" -proyectos Miteco- derivadas de proyecto subvencionado por el ministerio para la transición ecológica y el reto demográfico en aplicación del Real decreto 842/2024, de 27 de agosto,</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2026/D31000/006-013/00009</t>
+          <t>12054/2026</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2208,11 +2208,11 @@
         </is>
       </c>
       <c r="M17" s="6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>C6-3; C4-3</t>
+          <t>C*-3</t>
         </is>
       </c>
       <c r="O17" s="7" t="n">
@@ -2220,19 +2220,19 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Oferta Técnica 25 (JV) | Precio 75</t>
+          <t>Procedencia de materiales y proveedores 4 (JV) | Compromiso de reducción del plazo de ejecución de la obra 25 | Recursos: personal, maquinaria y medios auxiliares 7 (JV) | Mejoras sociales de inserción 10 | Propuesta Plan de Obra 5 (JV) | Organización de los trabajos 5 (JV) | Ampliación de garantía 10 | Mejoras ambientales y/o de accesibilidad 20 | Propuesta del Plan de Aseguramiento de la Calidad 4 (JV) | Medidas medioambientales 10</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>complementaria 5%; definitiva 5%</t>
+          <t>definitiva 5%</t>
         </is>
       </c>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="4" t="n"/>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45214000</t>
+          <t>45200000</t>
         </is>
       </c>
       <c r="U17" s="8" t="inlineStr">
@@ -2258,17 +2258,17 @@
     <row r="18">
       <c r="A18" s="2" t="n"/>
       <c r="B18" s="3" t="n">
-        <v>46323.04097222222</v>
+        <v>46321.99930555555</v>
       </c>
       <c r="C18" s="4">
         <f>IF(B18="","",INT(B18)-TODAY())</f>
         <v/>
       </c>
       <c r="D18" s="5" t="n">
-        <v>547041.28</v>
+        <v>1025843.16</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>547041.28</v>
+        <v>1025843.16</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -2277,27 +2277,27 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Alhaurín el Grande</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Consejo de Administración de la Agencia de Régimen Especial Ciclo Integral Aguas del Retortillo</t>
+          <t>Alcaldía del Ayuntamiento de Alhaurín el Grande</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>PAS/OBRAS/007/2026 Obras construcción EDAR Natural Puerto de la Encina</t>
+          <t>Proyecto de obras de renaturalización de las Avenidas Blas Infante y Libertad. Tramo 4</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1009/2026</t>
+          <t>25734/2026 BLAS INFANTE Y LIBERTAD</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2306,19 +2306,15 @@
         </is>
       </c>
       <c r="M18" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>E1-3</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="N18" s="2" t="n"/>
       <c r="O18" s="7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Calidad: Ampliación Garantía 6 | Calidad. Experiencia Jefe de Obras 10 | PRECIO 84</t>
+          <t>Proposición económica 80 | Memoria constructiva y programa de trabajo 4 (JV) | Medidas para reducir el impacto Ambiental 2 (JV) | Medidas para reducir el impacto urbano de la obra 4 (JV) | ampliación en el plazo de garantía 10</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2330,7 +2326,7 @@
       <c r="S18" s="4" t="n"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45252100</t>
+          <t>45223210; 45262520; 45233140; 45262210; 45112000; 45232100</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
@@ -2356,17 +2352,17 @@
     <row r="19">
       <c r="A19" s="2" t="n"/>
       <c r="B19" s="3" t="n">
-        <v>46323.5</v>
+        <v>46322.99930555555</v>
       </c>
       <c r="C19" s="4">
         <f>IF(B19="","",INT(B19)-TODAY())</f>
         <v/>
       </c>
       <c r="D19" s="5" t="n">
-        <v>794991.59</v>
+        <v>1408264.46</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>794991.59</v>
+        <v>1408264.46</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -2375,52 +2371,56 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Málaga</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Málaga</t>
-        </is>
-      </c>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Aena. Dirección del Aeropuerto de Málaga-Costa del Sol</t>
+          <t>Junta de Gobierno de la Diputación Provincial de Almería</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Ampliación Y Adecuación De Aseo 208 En El Aeropuerto De Málaga ¿ Costa Del Sol</t>
+          <t>Obras De Urbanización Para Un Complejo Deportivo. Vera 72PPOS24-27BI</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>AGP-147/2026</t>
+          <t>2026/D31000/006-013/00078</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>Normas internas</t>
+          <t>Abierto simplificado</t>
         </is>
       </c>
       <c r="M19" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="N19" s="2" t="n"/>
+        <v>12.2</v>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>G6-4</t>
+        </is>
+      </c>
       <c r="O19" s="7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>Precio 100</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="n"/>
+          <t>Oferta técnica 25 (JV) | Precio 75</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>definitiva 5%; complementaria 5%</t>
+        </is>
+      </c>
       <c r="R19" s="2" t="n"/>
       <c r="S19" s="4" t="n"/>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45211310</t>
+          <t>45233200</t>
         </is>
       </c>
       <c r="U19" s="8" t="inlineStr">
@@ -2446,46 +2446,42 @@
     <row r="20">
       <c r="A20" s="2" t="n"/>
       <c r="B20" s="3" t="n">
-        <v>46323.5</v>
+        <v>46322.99930555555</v>
       </c>
       <c r="C20" s="4">
         <f>IF(B20="","",INT(B20)-TODAY())</f>
         <v/>
       </c>
       <c r="D20" s="5" t="n">
-        <v>653963.23</v>
+        <v>826446.28</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>653963.23</v>
+        <v>826446.28</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Alicante</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Almoradí</t>
-        </is>
-      </c>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno del Ayuntamiento de Almoradí</t>
+          <t>Junta de Gobierno de la Diputación Provincial de Almería</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Mejora de la accesibilidad y la escena urbana en el entorno del Teatro Cortés y Museo del Terremoto (Plan de Actuación Integrado PAI, cofinanciado con la Unión Europea - FEDER)</t>
+          <t>Rehabilitación Y Mejora De Edificios Municipales. Benahadux 19PPOS24-27BII</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6981/2026</t>
+          <t>2026/D31000/006-013/00009</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2494,15 +2490,19 @@
         </is>
       </c>
       <c r="M20" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N20" s="2" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>C6-3; C4-3</t>
+        </is>
+      </c>
       <c r="O20" s="7" t="n">
         <v>0.25</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Proposición económica 75 | Memoria Técnica 25 (JV)</t>
+          <t>Oferta Técnica 25 (JV) | Precio 75</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       <c r="S20" s="4" t="n"/>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45233200; 45000000; 45111100; 45233140; 45233253; 45211360</t>
+          <t>45214000</t>
         </is>
       </c>
       <c r="U20" s="8" t="inlineStr">
@@ -2522,7 +2522,11 @@
           <t>PCAP</t>
         </is>
       </c>
-      <c r="V20" s="2" t="n"/>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>PPT</t>
+        </is>
+      </c>
       <c r="W20" s="8" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -2536,17 +2540,17 @@
     <row r="21">
       <c r="A21" s="2" t="n"/>
       <c r="B21" s="3" t="n">
-        <v>46323.5</v>
+        <v>46323.04097222222</v>
       </c>
       <c r="C21" s="4">
         <f>IF(B21="","",INT(B21)-TODAY())</f>
         <v/>
       </c>
       <c r="D21" s="5" t="n">
-        <v>590000</v>
+        <v>547041.28</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>590000</v>
+        <v>547041.28</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -2555,48 +2559,60 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Cádiz</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="n"/>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Comité Central de Compras de Navantia S.A., S.M.E.</t>
+          <t>Consejo de Administración de la Agencia de Régimen Especial Ciclo Integral Aguas del Retortillo</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Licitación para la adjudicación de un Contrato para los trabajos de rehabilitación de accesos, protecciones colectivas y líneas de vida en grúas en Navantia Cádiz.</t>
+          <t>PAS/OBRAS/007/2026 Obras construcción EDAR Natural Puerto de la Encina</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5100075545 Líneas Vida Grúas Navantia Cádiz</t>
+          <t>1009/2026</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>Normas internas</t>
+          <t>Abierto simplificado</t>
         </is>
       </c>
       <c r="M21" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="N21" s="2" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>E1-3</t>
+        </is>
+      </c>
       <c r="O21" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Según PPT y PCP 100 (JV)</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="n"/>
+          <t>Calidad: Ampliación Garantía 6 | Calidad. Experiencia Jefe de Obras 10 | PRECIO 84</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>definitiva 5%</t>
+        </is>
+      </c>
       <c r="R21" s="2" t="n"/>
       <c r="S21" s="4" t="n"/>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45262600; 45340000</t>
+          <t>45252100</t>
         </is>
       </c>
       <c r="U21" s="8" t="inlineStr">
@@ -2622,63 +2638,63 @@
     <row r="22">
       <c r="A22" s="2" t="n"/>
       <c r="B22" s="3" t="n">
-        <v>46323.99930555555</v>
+        <v>46323.5</v>
       </c>
       <c r="C22" s="4">
         <f>IF(B22="","",INT(B22)-TODAY())</f>
         <v/>
       </c>
       <c r="D22" s="5" t="n">
-        <v>734951.3100000001</v>
+        <v>794991.59</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>734951.3100000001</v>
+        <v>794991.59</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="n"/>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Manises</t>
+          <t>Aena. Dirección del Aeropuerto de Málaga-Costa del Sol</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Reasfaltado de la travesia de Manises de la CV-370 desde Avenida dels Tranvies hasta la V-11 de acceso al aeropuerto y sustitución del alumbrado del puente de la CV-371 en el término de Manises</t>
+          <t>Ampliación Y Adecuación De Aseo 208 En El Aeropuerto De Málaga ¿ Costa Del Sol</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3034000P</t>
+          <t>AGP-147/2026</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Abierto simplificado</t>
+          <t>Normas internas</t>
         </is>
       </c>
       <c r="M22" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>G4-3</t>
-        </is>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="N22" s="2" t="n"/>
       <c r="O22" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Oferta económica 70 | Amplliación del plazo de garantia 30</t>
+          <t>Precio 100</t>
         </is>
       </c>
       <c r="Q22" s="2" t="n"/>
@@ -2686,7 +2702,7 @@
       <c r="S22" s="4" t="n"/>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45233222; 45233252; 45233223; 45233251; 34928530; 34991000; 50232100</t>
+          <t>45211310</t>
         </is>
       </c>
       <c r="U22" s="8" t="inlineStr">
@@ -2712,17 +2728,17 @@
     <row r="23">
       <c r="A23" s="2" t="n"/>
       <c r="B23" s="3" t="n">
-        <v>46323.99930555555</v>
+        <v>46323.5</v>
       </c>
       <c r="C23" s="4">
         <f>IF(B23="","",INT(B23)-TODAY())</f>
         <v/>
       </c>
       <c r="D23" s="5" t="n">
-        <v>812294</v>
+        <v>653963.23</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>812294</v>
+        <v>653963.23</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -2731,27 +2747,27 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Alicante</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>el Genovés</t>
+          <t>Almoradí</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Pleno del Ayuntamiento de Genovés</t>
+          <t>Junta de Gobierno del Ayuntamiento de Almoradí</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Construcción de un edificio de nueva planta, destinado a la población joven de la localidad, emplazado en calle Maestro Serrano nº 4 de El Genovés.</t>
+          <t>Mejora de la accesibilidad y la escena urbana en el entorno del Teatro Cortés y Museo del Terremoto (Plan de Actuación Integrado PAI, cofinanciado con la Unión Europea - FEDER)</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2222/2026</t>
+          <t>6981/2026</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2760,31 +2776,27 @@
         </is>
       </c>
       <c r="M23" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>C*-3</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N23" s="2" t="n"/>
       <c r="O23" s="7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Mejor oferta económica 100</t>
+          <t>Proposición económica 75 | Memoria Técnica 25 (JV)</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>definitiva 5%</t>
+          <t>complementaria 5%; definitiva 5%</t>
         </is>
       </c>
       <c r="R23" s="2" t="n"/>
       <c r="S23" s="4" t="n"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45000000; 45220000; 45200000</t>
+          <t>45233200; 45000000; 45111100; 45233140; 45233253; 45211360</t>
         </is>
       </c>
       <c r="U23" s="8" t="inlineStr">
@@ -2792,11 +2804,7 @@
           <t>PCAP</t>
         </is>
       </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>PPT</t>
-        </is>
-      </c>
+      <c r="V23" s="2" t="n"/>
       <c r="W23" s="8" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -2810,75 +2818,67 @@
     <row r="24">
       <c r="A24" s="2" t="n"/>
       <c r="B24" s="3" t="n">
-        <v>46323.99930555555</v>
+        <v>46323.5</v>
       </c>
       <c r="C24" s="4">
         <f>IF(B24="","",INT(B24)-TODAY())</f>
         <v/>
       </c>
       <c r="D24" s="5" t="n">
-        <v>675994.61</v>
+        <v>590000</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>743594.0699999999</v>
+        <v>590000</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="H24" s="2" t="n"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno del Ajuntament de València</t>
+          <t>Comité Central de Compras de Navantia S.A., S.M.E.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Ejecución de las Obras denominadas Limpieza y mantenimiento de las fachadas del Mercado Central de València.-</t>
+          <t>Licitación para la adjudicación de un Contrato para los trabajos de rehabilitación de accesos, protecciones colectivas y líneas de vida en grúas en Navantia Cádiz.</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>04101/2026/236-O</t>
+          <t>5100075545 Líneas Vida Grúas Navantia Cádiz</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Abierto simplificado</t>
+          <t>Normas internas</t>
         </is>
       </c>
       <c r="M24" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>K7-3</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="N24" s="2" t="n"/>
       <c r="O24" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>REDUCCIÓN DEL PLAZO DE EJECUCIÓN 20 | BAJA ECONÓMICA AL PRESUPUESTO BASE DE LICITACIÓN 40 | EXPERIENCIA PROFESIONAL ESPECÍFICA DE LAS PERSONAS INTEGRANTES DEL EQUIPO DE TRABAJO 30 | AMPLIACIÓN PLAZO DE GARANTIA 10</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>definitiva 5%</t>
-        </is>
-      </c>
+          <t>Según PPT y PCP 100 (JV)</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="n"/>
       <c r="R24" s="2" t="n"/>
       <c r="S24" s="4" t="n"/>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45213141</t>
+          <t>45262600; 45340000</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
@@ -2911,68 +2911,64 @@
         <v/>
       </c>
       <c r="D25" s="5" t="n">
-        <v>781690.8</v>
+        <v>734951.3100000001</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>781690.8</v>
+        <v>734951.3100000001</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Málaga</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Alhaurín el Grande</t>
-        </is>
-      </c>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Alhaurín el Grande</t>
+          <t>Alcaldía del Ayuntamiento de Manises</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Mejora del acabado final mediante la aplicación de capa de mezcla bituminosa en caliente y mejora de la red de abastecimiento en el camino viejo de Málaga y aledaños de Alhaurín el Grande</t>
+          <t>Reasfaltado de la travesia de Manises de la CV-370 desde Avenida dels Tranvies hasta la V-11 de acceso al aeropuerto y sustitución del alumbrado del puente de la CV-371 en el término de Manises</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>23202/2026 CAMINO VIEJO DE MALAGA</t>
+          <t>3034000P</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Abierto simplificado</t>
         </is>
       </c>
       <c r="M25" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="N25" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>G4-3</t>
+        </is>
+      </c>
       <c r="O25" s="7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Proposición económica 50 | Conocimiento del proyecto 15 (JV) | Programación y organización 15 (JV) | MEJORA EN EL PLAZO DE GARANTIA 20</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>definitiva 5%</t>
-        </is>
-      </c>
+          <t>Oferta económica 70 | Amplliación del plazo de garantia 30</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="n"/>
       <c r="R25" s="2" t="n"/>
       <c r="S25" s="4" t="n"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45233140</t>
+          <t>45233222; 45233252; 45233223; 45233251; 34928530; 34991000; 50232100</t>
         </is>
       </c>
       <c r="U25" s="8" t="inlineStr">
@@ -2998,42 +2994,46 @@
     <row r="26">
       <c r="A26" s="2" t="n"/>
       <c r="B26" s="3" t="n">
-        <v>46324.58333333334</v>
+        <v>46323.99930555555</v>
       </c>
       <c r="C26" s="4">
         <f>IF(B26="","",INT(B26)-TODAY())</f>
         <v/>
       </c>
       <c r="D26" s="5" t="n">
-        <v>743801.65</v>
+        <v>812294</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>743801.65</v>
+        <v>812294</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="n"/>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>el Genovés</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Alcaldia del Ayuntamiento de Pilas</t>
+          <t>Pleno del Ayuntamiento de Genovés</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Ejecución de la obra "Proyecto de reasfaltado 2026, de Pilas (Sevilla).</t>
+          <t>Construcción de un edificio de nueva planta, destinado a la población joven de la localidad, emplazado en calle Maestro Serrano nº 4 de El Genovés.</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>P4107500C-2026/000082-PAAS</t>
+          <t>2222/2026</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3042,11 +3042,11 @@
         </is>
       </c>
       <c r="M26" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>G4-3; G*-3</t>
+          <t>C*-3</t>
         </is>
       </c>
       <c r="O26" s="7" t="n">
@@ -3054,15 +3054,19 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Reducción del plazo de ejecución [2] 10 | Aspecto Económico (precio) [1] 75 | Mejoras [3] 15</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="n"/>
+          <t>Mejor oferta económica 100</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>definitiva 5%</t>
+        </is>
+      </c>
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="4" t="n"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45233222</t>
+          <t>45000000; 45220000; 45200000</t>
         </is>
       </c>
       <c r="U26" s="8" t="inlineStr">
@@ -3088,46 +3092,42 @@
     <row r="27">
       <c r="A27" s="2" t="n"/>
       <c r="B27" s="3" t="n">
-        <v>46324.99930555555</v>
+        <v>46323.99930555555</v>
       </c>
       <c r="C27" s="4">
         <f>IF(B27="","",INT(B27)-TODAY())</f>
         <v/>
       </c>
       <c r="D27" s="5" t="n">
-        <v>667189.24</v>
+        <v>675994.61</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>667189.24</v>
+        <v>743594.0699999999</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Huelva</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>ISLA CRISTINA</t>
-        </is>
-      </c>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Isla Cristina</t>
+          <t>Junta de Gobierno del Ajuntament de València</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Obras Proyecto de renovación y mejora de la eficiencia energética de las instalaciones de alumbrado público exterior del municipio de Isla Cristina.</t>
+          <t>Ejecución de las Obras denominadas Limpieza y mantenimiento de las fachadas del Mercado Central de València.-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5773/2026</t>
+          <t>04101/2026/236-O</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3136,19 +3136,19 @@
         </is>
       </c>
       <c r="M27" s="6" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>I1-3</t>
+          <t>K7-3</t>
         </is>
       </c>
       <c r="O27" s="7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Ampliación plazo garantía 10 | Calidad técnica de la propuesta de ejecución 25 (JV) | Oferta económica 60 | Primera intervención efectiva ante incidencias cubiertas por la garantía 5</t>
+          <t>REDUCCIÓN DEL PLAZO DE EJECUCIÓN 20 | BAJA ECONÓMICA AL PRESUPUESTO BASE DE LICITACIÓN 40 | EXPERIENCIA PROFESIONAL ESPECÍFICA DE LAS PERSONAS INTEGRANTES DEL EQUIPO DE TRABAJO 30 | AMPLIACIÓN PLAZO DE GARANTIA 10</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       <c r="S27" s="4" t="n"/>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>45316100; 45315600</t>
+          <t>45213141</t>
         </is>
       </c>
       <c r="U27" s="8" t="inlineStr">
@@ -3186,17 +3186,17 @@
     <row r="28">
       <c r="A28" s="2" t="n"/>
       <c r="B28" s="3" t="n">
-        <v>46324.99930555555</v>
+        <v>46323.99930555555</v>
       </c>
       <c r="C28" s="4">
         <f>IF(B28="","",INT(B28)-TODAY())</f>
         <v/>
       </c>
       <c r="D28" s="5" t="n">
-        <v>568417.8100000001</v>
+        <v>781690.8</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>568417.8100000001</v>
+        <v>781690.8</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -3205,48 +3205,44 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Huelva</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>BONARES</t>
+          <t>Alhaurín el Grande</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Alcaldia del Ayuntamiento de Bonares</t>
+          <t>Alcaldía del Ayuntamiento de Alhaurín el Grande</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Creación de aparcamiento y plaza pública ajardinada en Avda. Nuestra Señora del Rocío nº 3 de Bonares (Huelva</t>
+          <t>Mejora del acabado final mediante la aplicación de capa de mezcla bituminosa en caliente y mejora de la red de abastecimiento en el camino viejo de Málaga y aledaños de Alhaurín el Grande</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4654/2026</t>
+          <t>23202/2026 CAMINO VIEJO DE MALAGA</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>Abierto simplificado</t>
+          <t>Abierto</t>
         </is>
       </c>
       <c r="M28" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>C*-3</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="N28" s="2" t="n"/>
       <c r="O28" s="7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>REDUCCIÓN DEL PLAZO DE EJECUCIÓN 12 | OFERTA ECONÓMICA 68 | AUMENTO PLAZO DE GARANTÍA 20</t>
+          <t>Proposición económica 50 | Conocimiento del proyecto 15 (JV) | Programación y organización 15 (JV) | MEJORA EN EL PLAZO DE GARANTIA 20</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3254,15 +3250,11 @@
           <t>definitiva 5%</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>No se prevé la revisión de precios (Cláusula 6.9. del PCAP).</t>
-        </is>
-      </c>
+      <c r="R28" s="2" t="n"/>
       <c r="S28" s="4" t="n"/>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45220000; 45223000; 45000000</t>
+          <t>45233140</t>
         </is>
       </c>
       <c r="U28" s="8" t="inlineStr">
@@ -3288,17 +3280,17 @@
     <row r="29">
       <c r="A29" s="2" t="n"/>
       <c r="B29" s="3" t="n">
-        <v>46324.99930555555</v>
+        <v>46324.58333333334</v>
       </c>
       <c r="C29" s="4">
         <f>IF(B29="","",INT(B29)-TODAY())</f>
         <v/>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1170584.07</v>
+        <v>743801.65</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1170584.07</v>
+        <v>743801.65</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -3313,17 +3305,17 @@
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Pleno del Ayuntamiento de La Roda de Andalucía</t>
+          <t>Alcaldia del Ayuntamiento de Pilas</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Contrato de obras para ejecución del "Proyecto básico y de terminación del pabellón polideportivo cubierto municipal"</t>
+          <t>Ejecución de la obra "Proyecto de reasfaltado 2026, de Pilas (Sevilla).</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>P4108200I-2026/000011-PAAS</t>
+          <t>P4107500C-2026/000082-PAAS</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3332,11 +3324,11 @@
         </is>
       </c>
       <c r="M29" s="6" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>C4-3</t>
+          <t>G4-3; G*-3</t>
         </is>
       </c>
       <c r="O29" s="7" t="n">
@@ -3344,7 +3336,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Aspecto Económico (precio) [1] 100</t>
+          <t>Reducción del plazo de ejecución [2] 10 | Aspecto Económico (precio) [1] 75 | Mejoras [3] 15</t>
         </is>
       </c>
       <c r="Q29" s="2" t="n"/>
@@ -3352,7 +3344,7 @@
       <c r="S29" s="4" t="n"/>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>45000000</t>
+          <t>45233222</t>
         </is>
       </c>
       <c r="U29" s="8" t="inlineStr">
@@ -3378,17 +3370,17 @@
     <row r="30">
       <c r="A30" s="2" t="n"/>
       <c r="B30" s="3" t="n">
-        <v>46325.58333333334</v>
+        <v>46324.99930555555</v>
       </c>
       <c r="C30" s="4">
         <f>IF(B30="","",INT(B30)-TODAY())</f>
         <v/>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1540129.68</v>
+        <v>667189.24</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1540129.68</v>
+        <v>667189.24</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -3397,27 +3389,27 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>ISLA CRISTINA</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Secretaría General de la Agencia Estatal Consejo Superior de Investigaciones Científicas</t>
+          <t>Alcaldía del Ayuntamiento de Isla Cristina</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Obras de nuevo edificio del Instituto de Astrofísica de Andalucía</t>
+          <t>Obras Proyecto de renovación y mejora de la eficiencia energética de las instalaciones de alumbrado público exterior del municipio de Isla Cristina.</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>35349/26</t>
+          <t>5773/2026</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3426,23 +3418,31 @@
         </is>
       </c>
       <c r="M30" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="N30" s="2" t="n"/>
+        <v>6.1</v>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>I1-3</t>
+        </is>
+      </c>
       <c r="O30" s="7" t="n">
         <v>0.25</v>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Documentación complementaria 4 (JV) | Características técnicas del control de calidad de la ejecución de la obra 3 (JV) | Plan de mantenimiento técnico-legal 15 | Estudio del proyecto 8 (JV) | Memoria de ejecución de las obras y análisis y programa de trabajos 10 (JV) | Porcentaje ofertado de control de calidad 8 | Ampliación del plazo de garantía 12 | Oferta economica 40</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="n"/>
+          <t>Ampliación plazo garantía 10 | Calidad técnica de la propuesta de ejecución 25 (JV) | Oferta económica 60 | Primera intervención efectiva ante incidencias cubiertas por la garantía 5</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>definitiva 5%</t>
+        </is>
+      </c>
       <c r="R30" s="2" t="n"/>
       <c r="S30" s="4" t="n"/>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>45214000; 45214600; 45213150</t>
+          <t>45316100; 45315600</t>
         </is>
       </c>
       <c r="U30" s="8" t="inlineStr">
@@ -3468,46 +3468,46 @@
     <row r="31">
       <c r="A31" s="2" t="n"/>
       <c r="B31" s="3" t="n">
-        <v>46328.33333333334</v>
+        <v>46324.99930555555</v>
       </c>
       <c r="C31" s="4">
         <f>IF(B31="","",INT(B31)-TODAY())</f>
         <v/>
       </c>
       <c r="D31" s="5" t="n">
-        <v>1189873.92</v>
+        <v>568417.8100000001</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>1189873.92</v>
+        <v>568417.8100000001</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Alicante</t>
+          <t>Huelva</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>ORIHUELA</t>
+          <t>BONARES</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno del Ayuntamiento de Orihuela</t>
+          <t>Alcaldia del Ayuntamiento de Bonares</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Rehabilitación de Paramentos y Acondicionamiento de Sala de hombres en el Museo Arqueológico Comarcal de Orihuela</t>
+          <t>Creación de aparcamiento y plaza pública ajardinada en Avda. Nuestra Señora del Rocío nº 3 de Bonares (Huelva</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>4727/2026 BIS</t>
+          <t>4654/2026</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3520,27 +3520,31 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>C*-3; K7-3</t>
+          <t>C*-3</t>
         </is>
       </c>
       <c r="O31" s="7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Ampliación del plazo de garantía 30 | OFERTA ECONÓMICA (Sin IVA) 45 | Estudio de unidades de obra del proyecto 15 (JV) | Estudio de mediciones del proyecto 10 (JV)</t>
+          <t>REDUCCIÓN DEL PLAZO DE EJECUCIÓN 12 | OFERTA ECONÓMICA 68 | AUMENTO PLAZO DE GARANTÍA 20</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>complementaria 5%; definitiva 5%</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="n"/>
+          <t>definitiva 5%</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>No se prevé la revisión de precios (Cláusula 6.9. del PCAP).</t>
+        </is>
+      </c>
       <c r="S31" s="4" t="n"/>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>45000000; 45454100; 45453000</t>
+          <t>45220000; 45223000; 45000000</t>
         </is>
       </c>
       <c r="U31" s="8" t="inlineStr">
@@ -3566,46 +3570,42 @@
     <row r="32">
       <c r="A32" s="2" t="n"/>
       <c r="B32" s="3" t="n">
-        <v>46328.58333333334</v>
+        <v>46324.99930555555</v>
       </c>
       <c r="C32" s="4">
         <f>IF(B32="","",INT(B32)-TODAY())</f>
         <v/>
       </c>
       <c r="D32" s="5" t="n">
-        <v>557102.23</v>
+        <v>1170584.07</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>557102.23</v>
+        <v>1170584.07</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>REQUENA</t>
-        </is>
-      </c>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno Local del Ayuntamiento de Requena</t>
+          <t>Pleno del Ayuntamiento de La Roda de Andalucía</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Demolicion y construccion Centro Social de Campo Arcís</t>
+          <t>Contrato de obras para ejecución del "Proyecto básico y de terminación del pabellón polideportivo cubierto municipal"</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2896352M</t>
+          <t>P4108200I-2026/000011-PAAS</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3614,27 +3614,27 @@
         </is>
       </c>
       <c r="M32" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="N32" s="2" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>C4-3</t>
+        </is>
+      </c>
       <c r="O32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Mejora en el Precio, 100 puntos 100</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>definitiva 5%</t>
-        </is>
-      </c>
+          <t>Aspecto Económico (precio) [1] 100</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="4" t="n"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>45211350; 45111100</t>
+          <t>45000000</t>
         </is>
       </c>
       <c r="U32" s="8" t="inlineStr">
@@ -3660,46 +3660,46 @@
     <row r="33">
       <c r="A33" s="2" t="n"/>
       <c r="B33" s="3" t="n">
-        <v>46328.58333333334</v>
+        <v>46325.58333333334</v>
       </c>
       <c r="C33" s="4">
         <f>IF(B33="","",INT(B33)-TODAY())</f>
         <v/>
       </c>
       <c r="D33" s="5" t="n">
-        <v>814296.7</v>
+        <v>1540129.68</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>814296.7</v>
+        <v>1540129.68</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Turís</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Turis</t>
+          <t>Secretaría General de la Agencia Estatal Consejo Superior de Investigaciones Científicas</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Urbanización calles perimetrales parcela nuevo CEIP</t>
+          <t>Obras de nuevo edificio del Instituto de Astrofísica de Andalucía</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3385/2026</t>
+          <t>35349/26</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -3708,27 +3708,23 @@
         </is>
       </c>
       <c r="M33" s="6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N33" s="2" t="n"/>
       <c r="O33" s="7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Precio 100</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>definitiva 5%</t>
-        </is>
-      </c>
+          <t>Documentación complementaria 4 (JV) | Características técnicas del control de calidad de la ejecución de la obra 3 (JV) | Plan de mantenimiento técnico-legal 15 | Estudio del proyecto 8 (JV) | Memoria de ejecución de las obras y análisis y programa de trabajos 10 (JV) | Porcentaje ofertado de control de calidad 8 | Ampliación del plazo de garantía 12 | Oferta economica 40</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="n"/>
       <c r="S33" s="4" t="n"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>45233140</t>
+          <t>45214000; 45214600; 45213150</t>
         </is>
       </c>
       <c r="U33" s="8" t="inlineStr">
@@ -3754,17 +3750,17 @@
     <row r="34">
       <c r="A34" s="2" t="n"/>
       <c r="B34" s="3" t="n">
-        <v>46328.99930555555</v>
+        <v>46328.33333333334</v>
       </c>
       <c r="C34" s="4">
         <f>IF(B34="","",INT(B34)-TODAY())</f>
         <v/>
       </c>
       <c r="D34" s="5" t="n">
-        <v>4502927.26</v>
+        <v>1189873.92</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>4502927.26</v>
+        <v>1189873.92</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -3773,28 +3769,32 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="n"/>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>ORIHUELA</t>
+        </is>
+      </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Pleno del Ayuntamiento de Carlet</t>
+          <t>Junta de Gobierno del Ayuntamiento de Orihuela</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Obras de restitución de las canalizaciones de la red de agua potable y de la red de saneamiento y pavimentación de la Ronda Malecón, financiadas con cargo al Fondo de Solidaridad de la Unión Europea</t>
+          <t>Rehabilitación de Paramentos y Acondicionamiento de Sala de hombres en el Museo Arqueológico Comarcal de Orihuela</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3018/2026</t>
+          <t>4727/2026 BIS</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Abierto simplificado</t>
         </is>
       </c>
       <c r="M34" s="6" t="n">
@@ -3802,27 +3802,27 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>E*-5</t>
+          <t>C*-3; K7-3</t>
         </is>
       </c>
       <c r="O34" s="7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Ampliación del plazo de garantía 10 | Uso de materiales con menor huella de carbono 20 | Reducción del plazo de ejecución 20 | Oferta económica 50</t>
+          <t>Ampliación del plazo de garantía 30 | OFERTA ECONÓMICA (Sin IVA) 45 | Estudio de unidades de obra del proyecto 15 (JV) | Estudio de mediciones del proyecto 10 (JV)</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>definitiva 5%</t>
+          <t>complementaria 5%; definitiva 5%</t>
         </is>
       </c>
       <c r="R34" s="2" t="n"/>
       <c r="S34" s="4" t="n"/>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>45240000; 45233200; 45232150; 45232440</t>
+          <t>45000000; 45454100; 45453000</t>
         </is>
       </c>
       <c r="U34" s="8" t="inlineStr">
@@ -3848,46 +3848,46 @@
     <row r="35">
       <c r="A35" s="2" t="n"/>
       <c r="B35" s="3" t="n">
-        <v>46329.58333333334</v>
+        <v>46328.58333333334</v>
       </c>
       <c r="C35" s="4">
         <f>IF(B35="","",INT(B35)-TODAY())</f>
         <v/>
       </c>
       <c r="D35" s="5" t="n">
-        <v>988010.83</v>
+        <v>557102.23</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>988010.83</v>
+        <v>557102.23</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Gines</t>
+          <t>REQUENA</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno Local del Ayuntamiento de Gines</t>
+          <t>Junta de Gobierno Local del Ayuntamiento de Requena</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Obras de rehabilitación y adecuación de inmueble municipal en plantas baja y sótano para aparcamiento público municipal y locales de usos culturales y sociales.</t>
+          <t>Demolicion y construccion Centro Social de Campo Arcís</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6859/2026</t>
+          <t>2896352M</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -3896,19 +3896,15 @@
         </is>
       </c>
       <c r="M35" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>C*-2</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N35" s="2" t="n"/>
       <c r="O35" s="7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>AMPLIACIÓN DEL PLAZO DE GARANTÍA DE LAS OBRAS 10 | VALORACIÓN DE RESIDUOS DE CONSTRUCCIÓN Y DEMOLICIÓN 5 | MEJORA 2: SISTEMA DE MONITORIZACIÓN ENERGÉTICA 5 | MEMORIA TÉCNICA DE EJECUCIÓN DE LA OBRA 10 (JV) | OFERTA ECONÓMICA 45 | PLAN DE MINIMIZACIÓN DE AFECCIONES AL ENTORNO 5 (JV) | PLAN DE COORDINACIÓN CON LA ACTIVIDAD MUNICIPAL Y LOS EQUIPAMIENTOS ADYACENTES 5 (JV) | MEJORA 1: CANALIZACIONES ADICIONALES 5 | CONTROL DE CALIDAD ADICIONAL 5 | PLAN DE INFORMACIÓN PÚBLICA Y DE GESTIÓN DE INCIDENCIAS 5 (JV)</t>
+          <t>Mejora en el Precio, 100 puntos 100</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -3920,7 +3916,7 @@
       <c r="S35" s="4" t="n"/>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>45453100; 45313100; 45331210</t>
+          <t>45211350; 45111100</t>
         </is>
       </c>
       <c r="U35" s="8" t="inlineStr">
@@ -3946,75 +3942,75 @@
     <row r="36">
       <c r="A36" s="2" t="n"/>
       <c r="B36" s="3" t="n">
-        <v>46329.79166666666</v>
+        <v>46328.58333333334</v>
       </c>
       <c r="C36" s="4">
         <f>IF(B36="","",INT(B36)-TODAY())</f>
         <v/>
       </c>
       <c r="D36" s="5" t="n">
-        <v>669122.0600000001</v>
+        <v>814296.7</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>669122.0600000001</v>
+        <v>814296.7</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Turís</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Presidencia del Consejo de Administración de la Empresa Provincial de Aguas de Córdoba S.A.</t>
+          <t>Alcaldía del Ayuntamiento de Turis</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Obra de Red de Abastecimiento Aldea del Villar (Fuente Palmera).</t>
+          <t>Urbanización calles perimetrales parcela nuevo CEIP</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>CC 55/2026</t>
+          <t>3385/2026</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Abierto simplificado</t>
         </is>
       </c>
       <c r="M36" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>E1-3</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N36" s="2" t="n"/>
       <c r="O36" s="7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Ampliación plazo de garantía 10 (JV) | Oferta económica 50 | Oferta técnica 40 (JV)</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="n"/>
+          <t>Precio 100</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>definitiva 5%</t>
+        </is>
+      </c>
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="4" t="n"/>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>45240000</t>
+          <t>45233140</t>
         </is>
       </c>
       <c r="U36" s="8" t="inlineStr">
@@ -4040,46 +4036,42 @@
     <row r="37">
       <c r="A37" s="2" t="n"/>
       <c r="B37" s="3" t="n">
-        <v>46329.79166666666</v>
+        <v>46328.99930555555</v>
       </c>
       <c r="C37" s="4">
         <f>IF(B37="","",INT(B37)-TODAY())</f>
         <v/>
       </c>
       <c r="D37" s="5" t="n">
-        <v>1071077.53</v>
+        <v>4502927.26</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1071077.53</v>
+        <v>4502927.26</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Almería</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Almería</t>
-        </is>
-      </c>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Presidencia de la Autoridad Portuaria de Almería</t>
+          <t>Pleno del Ayuntamiento de Carlet</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Obras de Reforma de Pasarelas 4 y 5 en Puerto de Almería</t>
+          <t>Obras de restitución de las canalizaciones de la red de agua potable y de la red de saneamiento y pavimentación de la Ronda Malecón, financiadas con cargo al Fondo de Solidaridad de la Unión Europea</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>31/O/A/AL26</t>
+          <t>3018/2026</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4092,23 +4084,27 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>C3-4</t>
+          <t>E*-5</t>
         </is>
       </c>
       <c r="O37" s="7" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Cuantitativos 75 | Cualitativos 25 (JV)</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="n"/>
+          <t>Ampliación del plazo de garantía 10 | Uso de materiales con menor huella de carbono 20 | Reducción del plazo de ejecución 20 | Oferta económica 50</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>definitiva 5%</t>
+        </is>
+      </c>
       <c r="R37" s="2" t="n"/>
       <c r="S37" s="4" t="n"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>45223210; 45223100</t>
+          <t>45240000; 45233200; 45232150; 45232440</t>
         </is>
       </c>
       <c r="U37" s="8" t="inlineStr">
@@ -4134,17 +4130,17 @@
     <row r="38">
       <c r="A38" s="2" t="n"/>
       <c r="B38" s="3" t="n">
-        <v>46329.79166666666</v>
+        <v>46329.58333333334</v>
       </c>
       <c r="C38" s="4">
         <f>IF(B38="","",INT(B38)-TODAY())</f>
         <v/>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1565254.69</v>
+        <v>988010.83</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1565254.69</v>
+        <v>988010.83</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -4153,32 +4149,32 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Gines</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Presidencia de la Autoridad Portuaria de Almería</t>
+          <t>Junta de Gobierno Local del Ayuntamiento de Gines</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Obras de reforma de Pasarelas 2 y 3 en Puerto de Almería</t>
+          <t>Obras de rehabilitación y adecuación de inmueble municipal en plantas baja y sótano para aparcamiento público municipal y locales de usos culturales y sociales.</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>26/O/A/AL26</t>
+          <t>6859/2026</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Abierto simplificado</t>
         </is>
       </c>
       <c r="M38" s="6" t="n">
@@ -4186,7 +4182,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>C3-4</t>
+          <t>C*-2</t>
         </is>
       </c>
       <c r="O38" s="7" t="n">
@@ -4194,15 +4190,19 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Cuantitativos 75 | Cualitativos 25 (JV)</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="n"/>
+          <t>AMPLIACIÓN DEL PLAZO DE GARANTÍA DE LAS OBRAS 10 | VALORACIÓN DE RESIDUOS DE CONSTRUCCIÓN Y DEMOLICIÓN 5 | MEJORA 2: SISTEMA DE MONITORIZACIÓN ENERGÉTICA 5 | MEMORIA TÉCNICA DE EJECUCIÓN DE LA OBRA 10 (JV) | OFERTA ECONÓMICA 45 | PLAN DE MINIMIZACIÓN DE AFECCIONES AL ENTORNO 5 (JV) | PLAN DE COORDINACIÓN CON LA ACTIVIDAD MUNICIPAL Y LOS EQUIPAMIENTOS ADYACENTES 5 (JV) | MEJORA 1: CANALIZACIONES ADICIONALES 5 | CONTROL DE CALIDAD ADICIONAL 5 | PLAN DE INFORMACIÓN PÚBLICA Y DE GESTIÓN DE INCIDENCIAS 5 (JV)</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>definitiva 5%</t>
+        </is>
+      </c>
       <c r="R38" s="2" t="n"/>
       <c r="S38" s="4" t="n"/>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>45223210; 45223100</t>
+          <t>45453100; 45313100; 45331210</t>
         </is>
       </c>
       <c r="U38" s="8" t="inlineStr">
@@ -4228,71 +4228,83 @@
     <row r="39">
       <c r="A39" s="2" t="n"/>
       <c r="B39" s="3" t="n">
-        <v>46329.99930555555</v>
+        <v>46329.58333333334</v>
       </c>
       <c r="C39" s="4">
         <f>IF(B39="","",INT(B39)-TODAY())</f>
         <v/>
       </c>
       <c r="D39" s="5" t="n">
-        <v>564012.4</v>
+        <v>392087954.71</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>564012.4</v>
+        <v>431296750.18</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Comunitat Valenciana</t>
         </is>
       </c>
-      <c r="G39" s="2" t="n"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Oliva</t>
+          <t>Castelló de la Plana</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Concejal de Contratación del Ayuntamiento de Oliva</t>
+          <t>Dirección General de Gestión Económica, Contratación e Infraestructuras de la Conselleria de Sanidad</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Mejora de la accesibilidad en espacios públicos y renovación de la red de abastecimiento de agua potable</t>
+          <t>Obras del Nuevo Hospital General Universitario de Castellón.</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>15056/2026</t>
+          <t>31/2027</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>Abierto simplificado</t>
+          <t>Abierto</t>
         </is>
       </c>
       <c r="M39" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N39" s="2" t="n"/>
+        <v>60</v>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>C*-6</t>
+        </is>
+      </c>
       <c r="O39" s="7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Ampliación adicional plazo de garantía 10 | Baja económica en el tipo de licitación 20 | Conjunto de mejoras 70</t>
+          <t>PROPOSICIÓN TÉCNICA 30 (JV) | PROPOSICIÓN ECONÓMICA 50 | SEGUIMIENTO Y CONTROL DE LA OBRA MEDIANTE NUEVAS TECNOLOGÍAS 5 | INCREMENTO PLAZO DE GARANTÍA 5 | CRITERIO MAYOR EXPERIENCIA DEL EQUIPO MÍNIMO DE TRABAJO 10</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>definitiva 5%; complementaria 2%</t>
-        </is>
-      </c>
-      <c r="R39" s="2" t="n"/>
+          <t>complementaria 5%; definitiva 5%</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>Recogida en el apartado H del Anexo I al PCAP.</t>
+        </is>
+      </c>
       <c r="S39" s="4" t="n"/>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>45200000</t>
+          <t>45215100</t>
         </is>
       </c>
       <c r="U39" s="8" t="inlineStr">
@@ -4318,17 +4330,17 @@
     <row r="40">
       <c r="A40" s="2" t="n"/>
       <c r="B40" s="3" t="n">
-        <v>46329.99930555555</v>
+        <v>46329.79166666666</v>
       </c>
       <c r="C40" s="4">
         <f>IF(B40="","",INT(B40)-TODAY())</f>
         <v/>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1106611.57</v>
+        <v>669122.0600000001</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>1106611.57</v>
+        <v>669122.0600000001</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -4337,44 +4349,48 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="n"/>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Alcalá del Río</t>
+          <t>Presidencia del Consejo de Administración de la Empresa Provincial de Aguas de Córdoba S.A.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Contrato de obras relativo al Proyecto básico y de ejecución de Reforma y Acondicionamiento de la Piscina Municipal y el entorno periférico</t>
+          <t>Obra de Red de Abastecimiento Aldea del Villar (Fuente Palmera).</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>P4100500J-2026/000021-PAAS</t>
+          <t>CC 55/2026</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>Abierto simplificado</t>
+          <t>Abierto</t>
         </is>
       </c>
       <c r="M40" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>J2-2; C3-2; C*-2; J*-2</t>
+          <t>E1-3</t>
         </is>
       </c>
       <c r="O40" s="7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Aspecto Económico (precio) [1] 40 | Mejora 1 Nuevo sistema de Riego para las zonas de césped [2] 20 | Mejora 2 Retirada y renovación del césped [3] 40</t>
+          <t>Ampliación plazo de garantía 10 (JV) | Oferta económica 50 | Oferta técnica 40 (JV)</t>
         </is>
       </c>
       <c r="Q40" s="2" t="n"/>
@@ -4382,7 +4398,7 @@
       <c r="S40" s="4" t="n"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>45212220</t>
+          <t>45240000</t>
         </is>
       </c>
       <c r="U40" s="8" t="inlineStr">
@@ -4408,17 +4424,17 @@
     <row r="41">
       <c r="A41" s="2" t="n"/>
       <c r="B41" s="3" t="n">
-        <v>46329.99930555555</v>
+        <v>46329.79166666666</v>
       </c>
       <c r="C41" s="4">
         <f>IF(B41="","",INT(B41)-TODAY())</f>
         <v/>
       </c>
       <c r="D41" s="5" t="n">
-        <v>3060580.6</v>
+        <v>1071077.53</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>3060580.6</v>
+        <v>1071077.53</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -4427,23 +4443,27 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Huelva</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="n"/>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Pleno del Ayuntamiento de Punta umbría</t>
+          <t>Presidencia de la Autoridad Portuaria de Almería</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Ejecución de las obras para la renovación y mejora de la eficiencia energética de las instalaciones de alumbrado público exterior en el Municipio de Punta Umbría (Huelva)</t>
+          <t>Obras de Reforma de Pasarelas 4 y 5 en Puerto de Almería</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>5163/2026</t>
+          <t>31/O/A/AL26</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4452,11 +4472,11 @@
         </is>
       </c>
       <c r="M41" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>I1-4</t>
+          <t>C3-4</t>
         </is>
       </c>
       <c r="O41" s="7" t="n">
@@ -4464,19 +4484,15 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Oferta económica 35 | Reducción de Plazos 20 | Experiencia Profesional 20 | Memoria Técnica 25 (JV)</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>definitiva 5%</t>
-        </is>
-      </c>
+          <t>Cuantitativos 75 | Cualitativos 25 (JV)</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="n"/>
       <c r="R41" s="2" t="n"/>
       <c r="S41" s="4" t="n"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>45316100; 34928500; 45315600</t>
+          <t>45223210; 45223100</t>
         </is>
       </c>
       <c r="U41" s="8" t="inlineStr">
@@ -4502,17 +4518,17 @@
     <row r="42">
       <c r="A42" s="2" t="n"/>
       <c r="B42" s="3" t="n">
-        <v>46329.99930555555</v>
+        <v>46329.79166666666</v>
       </c>
       <c r="C42" s="4">
         <f>IF(B42="","",INT(B42)-TODAY())</f>
         <v/>
       </c>
       <c r="D42" s="5" t="n">
-        <v>2370624.52</v>
+        <v>13104056.72</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>2844749.42</v>
+        <v>13104056.72</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -4521,23 +4537,23 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Junta de Gobierno Local del Ayuntamiento de El Ejido</t>
+          <t>Pleno del Ayuntamiento de Jaén</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Es objeto de la presente licitación es la contratación de la ejecución del proyecto de obras denominado: Proyecto de construcción de adecuación del complejo deportivo en el núcleo de Almerimar. Fase II, conforme a las especificaciones y características expuestas en el presente pliego y en el proyecto técnico.</t>
+          <t>Contratación de las obras de reparación de pavimentos de calles del municipio de Jaén tras concatenación de borrascas durante los meses de enero y febrero de 2026, financiadas por la Administración General del Estado, a través del Ministerio de Política Territorial y Memoria Democrática, al amparo del art. 7 del Real Decreto-Ley 5/2026, de 17 de febrero.</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2026 1137</t>
+          <t>2026000083</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -4546,7 +4562,7 @@
         </is>
       </c>
       <c r="M42" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N42" s="2" t="n"/>
       <c r="O42" s="7" t="n">
@@ -4554,19 +4570,21 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Proposición económica 75 | Criterios evaluables mediante un juicio de valor 25 (JV)</t>
+          <t>Proceso constructivo 10 (JV) | Precio 55 | Disponibilidad para trabajos nocturnos 10 | Programa de trabajo 15 (JV) | Plazo de garantía 10</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>provisional 5%</t>
+          <t>definitiva 5%</t>
         </is>
       </c>
       <c r="R42" s="2" t="n"/>
-      <c r="S42" s="4" t="n"/>
+      <c r="S42" s="4" t="n">
+        <v>6</v>
+      </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>45200000</t>
+          <t>45233252; 45111100; 45262300; 45262522</t>
         </is>
       </c>
       <c r="U42" s="8" t="inlineStr">
@@ -4592,17 +4610,17 @@
     <row r="43">
       <c r="A43" s="2" t="n"/>
       <c r="B43" s="3" t="n">
-        <v>46331.99930555555</v>
+        <v>46329.79166666666</v>
       </c>
       <c r="C43" s="4">
         <f>IF(B43="","",INT(B43)-TODAY())</f>
         <v/>
       </c>
       <c r="D43" s="5" t="n">
-        <v>2543636.15</v>
+        <v>1565254.69</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>2543636.15</v>
+        <v>1565254.69</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -4611,23 +4629,27 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="n"/>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Presidencia de la Diputación Provincial de Sevilla</t>
+          <t>Presidencia de la Autoridad Portuaria de Almería</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Obra para la mejora de la estación de bombeo de agua potable al Consorcio de Aguas Sierra Sur, nuevo depósito y sistemas antiariete, Osuna</t>
+          <t>Obras de reforma de Pasarelas 2 y 3 en Puerto de Almería</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>2026/000697-PAA</t>
+          <t>26/O/A/AL26</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -4636,11 +4658,11 @@
         </is>
       </c>
       <c r="M43" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>E1-5</t>
+          <t>C3-4</t>
         </is>
       </c>
       <c r="O43" s="7" t="n">
@@ -4648,7 +4670,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Calidad [1] 25 (JV) | Aspecto Económico (precio) [1] 75</t>
+          <t>Cuantitativos 75 | Cualitativos 25 (JV)</t>
         </is>
       </c>
       <c r="Q43" s="2" t="n"/>
@@ -4656,7 +4678,7 @@
       <c r="S43" s="4" t="n"/>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>45213260; 45232152</t>
+          <t>45223210; 45223100</t>
         </is>
       </c>
       <c r="U43" s="8" t="inlineStr">
@@ -4682,42 +4704,42 @@
     <row r="44">
       <c r="A44" s="2" t="n"/>
       <c r="B44" s="3" t="n">
-        <v>46332.99930555555</v>
+        <v>46329.99930555555</v>
       </c>
       <c r="C44" s="4">
         <f>IF(B44="","",INT(B44)-TODAY())</f>
         <v/>
       </c>
       <c r="D44" s="5" t="n">
-        <v>1089694.08</v>
+        <v>564012.4</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>1089694.08</v>
+        <v>564012.4</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Andalucía</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="n"/>
+          <t>Comunitat Valenciana</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Oliva</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Alcaldia del Ayuntamiento de San Nicolás del Puerto</t>
+          <t>Concejal de Contratación del Ayuntamiento de Oliva</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>PAS. Construcción de Piscina Municipal y de vesturarios en San Nicolás del Puerto. Plan ACTUA 2022 Diputación.</t>
+          <t>Mejora de la accesibilidad en espacios públicos y renovación de la red de abastecimiento de agua potable</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>P4108800F-2026/000032-PAAS</t>
+          <t>15056/2026</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -4726,27 +4748,27 @@
         </is>
       </c>
       <c r="M44" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>C6-6; C*-4; C4-4</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N44" s="2" t="n"/>
       <c r="O44" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Aspecto Económico (precio) [1] 100</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="n"/>
+          <t>Ampliación adicional plazo de garantía 10 | Baja económica en el tipo de licitación 20 | Conjunto de mejoras 70</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>definitiva 5%; complementaria 2%</t>
+        </is>
+      </c>
       <c r="R44" s="2" t="n"/>
       <c r="S44" s="4" t="n"/>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>45000000</t>
+          <t>45200000</t>
         </is>
       </c>
       <c r="U44" s="8" t="inlineStr">
@@ -4772,17 +4794,17 @@
     <row r="45">
       <c r="A45" s="2" t="n"/>
       <c r="B45" s="3" t="n">
-        <v>46335.99930555555</v>
+        <v>46329.99930555555</v>
       </c>
       <c r="C45" s="4">
         <f>IF(B45="","",INT(B45)-TODAY())</f>
         <v/>
       </c>
       <c r="D45" s="5" t="n">
-        <v>929839.95</v>
+        <v>1106611.57</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>929839.95</v>
+        <v>1106611.57</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -4791,56 +4813,52 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Córdoba</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>CABRA</t>
-        </is>
-      </c>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Alcaldía del Ayuntamiento de Cabra</t>
+          <t>Alcaldía del Ayuntamiento de Alcalá del Río</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Servicio de redacción del proyecto básico y ejecución de obras, coordinación en materia de seguridad y salud durante la elaboración del proyecto, estudio de libro del edificio y la posterior ejecución de las obras de construcción de seis viviendas en alquiler social en edificios energéticamente eficientes, en el marco del capítulo VII del real decreto 853/2021 de 5 de octubre</t>
+          <t>Contrato de obras relativo al Proyecto básico y de ejecución de Reforma y Acondicionamiento de la Piscina Municipal y el entorno periférico</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>2026/21080</t>
+          <t>P4100500J-2026/000021-PAAS</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Abierto simplificado</t>
         </is>
       </c>
       <c r="M45" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="N45" s="2" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>J2-2; C3-2; C*-2; J*-2</t>
+        </is>
+      </c>
       <c r="O45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Redacción proyecto en formato BIM 10 | Menor precio ofertado sobre el precio de licitación, hasta un máximo de 75 puntos. 75 | Compromiso de Ampliación de Plazo de Garantía 15</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>definitiva 5%</t>
-        </is>
-      </c>
+          <t>Aspecto Económico (precio) [1] 40 | Mejora 1 Nuevo sistema de Riego para las zonas de césped [2] 20 | Mejora 2 Retirada y renovación del césped [3] 40</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="n"/>
       <c r="R45" s="2" t="n"/>
       <c r="S45" s="4" t="n"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>45211000; 71200000</t>
+          <t>45212220</t>
         </is>
       </c>
       <c r="U45" s="8" t="inlineStr">
@@ -4866,46 +4884,42 @@
     <row r="46">
       <c r="A46" s="2" t="n"/>
       <c r="B46" s="3" t="n">
-        <v>46335.99930555555</v>
+        <v>46329.99930555555</v>
       </c>
       <c r="C46" s="4">
         <f>IF(B46="","",INT(B46)-TODAY())</f>
         <v/>
       </c>
       <c r="D46" s="5" t="n">
-        <v>4895758.65</v>
+        <v>3060580.6</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>4895758.65</v>
+        <v>3060580.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Estivella</t>
-        </is>
-      </c>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Pleno del Ayuntamiento de Estivella</t>
+          <t>Pleno del Ayuntamiento de Punta umbría</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Demolició i reposició del CENTRE CEIP EL BRAÇAL en la mateixa parcel·la</t>
+          <t>Ejecución de las obras para la renovación y mejora de la eficiencia energética de las instalaciones de alumbrado público exterior en el Municipio de Punta Umbría (Huelva)</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>271/2026</t>
+          <t>5163/2026</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -4914,19 +4928,19 @@
         </is>
       </c>
       <c r="M46" s="6" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>C*-5</t>
+          <t>I1-4</t>
         </is>
       </c>
       <c r="O46" s="7" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Planificación de los trabajos y conocimiento del proyecto (Hasta 5 puntos) 5 (JV) | Aumento del plazo de garantía 2 | Compromiso de realización de un reportaje fotográfico de la obra terminada 4 | Medidas para la reducción de los impactos generados en el entorno durante el proceso constructivo (Hasta 5 puntos) 5 (JV) | Compromiso de limpieza fina de obra 3 | Implantación y organización de la obra (Hasta 10 puntos) 10 (JV) | Compromiso de calidad en personal asignado 6 | Menor precio ofertado 65</t>
+          <t>Oferta económica 35 | Reducción de Plazos 20 | Experiencia Profesional 20 | Memoria Técnica 25 (JV)</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -4934,15 +4948,11 @@
           <t>definitiva 5%</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>Conforme al artículo 10 del PCAP.</t>
-        </is>
-      </c>
+      <c r="R46" s="2" t="n"/>
       <c r="S46" s="4" t="n"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>45214000</t>
+          <t>45316100; 34928500; 45315600</t>
         </is>
       </c>
       <c r="U46" s="8" t="inlineStr">
@@ -4968,17 +4978,17 @@
     <row r="47">
       <c r="A47" s="2" t="n"/>
       <c r="B47" s="3" t="n">
-        <v>46335.99930555555</v>
+        <v>46329.99930555555</v>
       </c>
       <c r="C47" s="4">
         <f>IF(B47="","",INT(B47)-TODAY())</f>
         <v/>
       </c>
       <c r="D47" s="5" t="n">
-        <v>4566296.26</v>
+        <v>2370624.52</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>4566296.26</v>
+        <v>2844749.42</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -4987,27 +4997,23 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>OGIJARES</t>
-        </is>
-      </c>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Presidencia de la Diputación Provincial de Granada</t>
+          <t>Junta de Gobierno Local del Ayuntamiento de El Ejido</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Refundido final urbanización del Plan Especial "La Aurora" en Ogíjares.</t>
+          <t>Es objeto de la presente licitación es la contratación de la ejecución del proyecto de obras denominado: Proyecto de construcción de adecuación del complejo deportivo en el núcleo de Almerimar. Fase II, conforme a las especificaciones y características expuestas en el presente pliego y en el proyecto técnico.</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>OB-037/26</t>
+          <t>2026 1137</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -5016,31 +5022,27 @@
         </is>
       </c>
       <c r="M47" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>I9-4; G6-5; E7-5</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="N47" s="2" t="n"/>
       <c r="O47" s="7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>El precio más bajo 90 | Ampliación del plazo de garantía 10</t>
+          <t>Proposición económica 75 | Criterios evaluables mediante un juicio de valor 25 (JV)</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>definitiva 5%</t>
+          <t>provisional 5%</t>
         </is>
       </c>
       <c r="R47" s="2" t="n"/>
       <c r="S47" s="4" t="n"/>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>45220000; 45233140; 45232200; 45233252; 45232150; 45232410; 45316110</t>
+          <t>45200000</t>
         </is>
       </c>
       <c r="U47" s="8" t="inlineStr">
@@ -5066,17 +5068,17 @@
     <row r="48">
       <c r="A48" s="2" t="n"/>
       <c r="B48" s="3" t="n">
-        <v>46335.99930555555</v>
+        <v>46331.99930555555</v>
       </c>
       <c r="C48" s="4">
         <f>IF(B48="","",INT(B48)-TODAY())</f>
         <v/>
       </c>
       <c r="D48" s="5" t="n">
-        <v>1793227</v>
+        <v>2543636.15</v>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1793227</v>
+        <v>2543636.15</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -5085,23 +5087,23 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="H48" s="2" t="n"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Dirección Gerente de la Empresa Municipal de Abastecimiento y Saneamiento de Granada, S.A.</t>
+          <t>Presidencia de la Diputación Provincial de Sevilla</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Mejora de las infraestructuras y resiliencia hídrica en el ciclo integral del agua en la Avenida Don Bosco, entre la Avenida de Cádiz y la Avenida Fernando de los Ríos (Granada).</t>
+          <t>Obra para la mejora de la estación de bombeo de agua potable al Consorcio de Aguas Sierra Sur, nuevo depósito y sistemas antiariete, Osuna</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Obra 2025-00017_3</t>
+          <t>2026/000697-PAA</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -5110,19 +5112,19 @@
         </is>
       </c>
       <c r="M48" s="6" t="n">
-        <v>144</v>
+        <v>8</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>E*-4</t>
+          <t>E1-5</t>
         </is>
       </c>
       <c r="O48" s="7" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Oferta económica 60 | Oferta técnica 40 (JV)</t>
+          <t>Calidad [1] 25 (JV) | Aspecto Económico (precio) [1] 75</t>
         </is>
       </c>
       <c r="Q48" s="2" t="n"/>
@@ -5130,7 +5132,7 @@
       <c r="S48" s="4" t="n"/>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>45232150</t>
+          <t>45213260; 45232152</t>
         </is>
       </c>
       <c r="U48" s="8" t="inlineStr">
@@ -5156,17 +5158,17 @@
     <row r="49">
       <c r="A49" s="2" t="n"/>
       <c r="B49" s="3" t="n">
-        <v>46350.45833333334</v>
+        <v>46332.99930555555</v>
       </c>
       <c r="C49" s="4">
         <f>IF(B49="","",INT(B49)-TODAY())</f>
         <v/>
       </c>
       <c r="D49" s="5" t="n">
-        <v>3246355.87</v>
+        <v>1089694.08</v>
       </c>
       <c r="E49" s="5" t="n">
-        <v>3246355.87</v>
+        <v>1089694.08</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -5181,30 +5183,30 @@
       <c r="H49" s="2" t="n"/>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Comisión Ejecutiva de la Gerencia de Urbanismo de Sevilla</t>
+          <t>Alcaldia del Ayuntamiento de San Nicolás del Puerto</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Obras del Proyecto básico y de ejecución para rehabilitación, consolidación y puesta en valor de la sala de Profundis y las viviendas anexas del Real Monasterio de Santa Clara.</t>
+          <t>PAS. Construcción de Piscina Municipal y de vesturarios en San Nicolás del Puerto. Plan ACTUA 2022 Diputación.</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>19/2026</t>
+          <t>P4108800F-2026/000032-PAAS</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Abierto simplificado</t>
         </is>
       </c>
       <c r="M49" s="6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>K7-4</t>
+          <t>C6-6; C*-4; C4-4</t>
         </is>
       </c>
       <c r="O49" s="7" t="n">
@@ -5212,23 +5214,15 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1. OFERTA ECONÓMICA 20 | 2. MAYOR CUALIFICACIÓN Y EXPERIENCIA DEL EQUIPO TÉCNICO. SUBCRITERIO D. BAREMACIÓN DEL PERFIL 4 RESTAURADOR. 10 | 3. AMPLIACIÓN DEL PLAZO DE GARANTÍA. 30 | 2. MAYOR CUALIFICACIÓN Y EXPERIENCIA DEL EQUIPO TÉCNICO. SUBCRITERIO B. BAREMACIÓN DEL PERFIL 2. ENCARGADO. 15 | 2. MAYOR CUALIFICACIÓN Y EXPERIENCIA DEL EQUIPO TÉCNICO. SUBCRITERIO C. BAREMACIÓN DEL PERFIL 3. TÉCNICO EN PREVENCIÓN DE RIESGOS LABORALES. 10 | 2. MAYOR CUALIFICACIÓN Y EXPERIENCIA DEL EQUIPO TÉCNICO. SUBCRITERIO A. BAREMACIÓN DEL PERFIL 1. TÉCNICO JEFE DE OBRA. 15</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>definitiva 5%; complementaria 5%</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>FÓRMULA 831. Obras de restauración de edificios.</t>
-        </is>
-      </c>
+          <t>Aspecto Económico (precio) [1] 100</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="n"/>
+      <c r="R49" s="2" t="n"/>
       <c r="S49" s="4" t="n"/>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>45212300</t>
+          <t>45000000</t>
         </is>
       </c>
       <c r="U49" s="8" t="inlineStr">
@@ -5236,7 +5230,11 @@
           <t>PCAP</t>
         </is>
       </c>
-      <c r="V49" s="2" t="n"/>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>PPT</t>
+        </is>
+      </c>
       <c r="W49" s="8" t="inlineStr">
         <is>
           <t>Ver</t>
@@ -5250,17 +5248,17 @@
     <row r="50">
       <c r="A50" s="2" t="n"/>
       <c r="B50" s="3" t="n">
-        <v>48099.58333333334</v>
+        <v>46335.99930555555</v>
       </c>
       <c r="C50" s="4">
         <f>IF(B50="","",INT(B50)-TODAY())</f>
         <v/>
       </c>
       <c r="D50" s="5" t="n">
-        <v>3000000</v>
+        <v>929839.95</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>3000000</v>
+        <v>929839.95</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -5274,71 +5272,549 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>CABRA</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Consejo de Administración de la Empresa Municipal de Aguas de Córdoba, S.A. (EMACSA)</t>
+          <t>Alcaldía del Ayuntamiento de Cabra</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Sistema dinámico de adquisición de obras en redes e instalaciones para la Empresa Municipal de Aguas de Córdoba, S.A.</t>
+          <t>Servicio de redacción del proyecto básico y ejecución de obras, coordinación en materia de seguridad y salud durante la elaboración del proyecto, estudio de libro del edificio y la posterior ejecución de las obras de construcción de seis viviendas en alquiler social en edificios energéticamente eficientes, en el marco del capítulo VII del real decreto 853/2021 de 5 de octubre</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>SDA32/2026</t>
+          <t>2026/21080</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Restringido</t>
-        </is>
-      </c>
-      <c r="M50" s="6" t="n"/>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>12</v>
+      </c>
       <c r="N50" s="2" t="n"/>
       <c r="O50" s="7" t="n">
         <v>0</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
+          <t>Redacción proyecto en formato BIM 10 | Menor precio ofertado sobre el precio de licitación, hasta un máximo de 75 puntos. 75 | Compromiso de Ampliación de Plazo de Garantía 15</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>definitiva 5%</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="n"/>
+      <c r="S50" s="4" t="n"/>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>45211000; 71200000</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>PCAP</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>PPT</t>
+        </is>
+      </c>
+      <c r="W50" s="8" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+      <c r="X50" s="9" t="n">
+        <v>46310</v>
+      </c>
+      <c r="Y50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="3" t="n">
+        <v>46335.99930555555</v>
+      </c>
+      <c r="C51" s="4">
+        <f>IF(B51="","",INT(B51)-TODAY())</f>
+        <v/>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>4895758.65</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>4895758.65</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Comunitat Valenciana</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Estivella</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Pleno del Ayuntamiento de Estivella</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Demolició i reposició del CENTRE CEIP EL BRAÇAL en la mateixa parcel·la</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>271/2026</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="M51" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>C*-5</t>
+        </is>
+      </c>
+      <c r="O51" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>Planificación de los trabajos y conocimiento del proyecto (Hasta 5 puntos) 5 (JV) | Aumento del plazo de garantía 2 | Compromiso de realización de un reportaje fotográfico de la obra terminada 4 | Medidas para la reducción de los impactos generados en el entorno durante el proceso constructivo (Hasta 5 puntos) 5 (JV) | Compromiso de limpieza fina de obra 3 | Implantación y organización de la obra (Hasta 10 puntos) 10 (JV) | Compromiso de calidad en personal asignado 6 | Menor precio ofertado 65</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>definitiva 5%</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>Conforme al artículo 10 del PCAP.</t>
+        </is>
+      </c>
+      <c r="S51" s="4" t="n"/>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>45214000</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>PCAP</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>PPT</t>
+        </is>
+      </c>
+      <c r="W51" s="8" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+      <c r="X51" s="9" t="n">
+        <v>46310</v>
+      </c>
+      <c r="Y51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="3" t="n">
+        <v>46335.99930555555</v>
+      </c>
+      <c r="C52" s="4">
+        <f>IF(B52="","",INT(B52)-TODAY())</f>
+        <v/>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>4566296.26</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>4566296.26</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>OGIJARES</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Presidencia de la Diputación Provincial de Granada</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Refundido final urbanización del Plan Especial "La Aurora" en Ogíjares.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>OB-037/26</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>I9-4; G6-5; E7-5</t>
+        </is>
+      </c>
+      <c r="O52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>El precio más bajo 90 | Ampliación del plazo de garantía 10</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>definitiva 5%</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="n"/>
+      <c r="S52" s="4" t="n"/>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>45220000; 45233140; 45232200; 45233252; 45232150; 45232410; 45316110</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>PCAP</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>PPT</t>
+        </is>
+      </c>
+      <c r="W52" s="8" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+      <c r="X52" s="9" t="n">
+        <v>46310</v>
+      </c>
+      <c r="Y52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="3" t="n">
+        <v>46335.99930555555</v>
+      </c>
+      <c r="C53" s="4">
+        <f>IF(B53="","",INT(B53)-TODAY())</f>
+        <v/>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>1793227</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>1793227</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Dirección Gerente de la Empresa Municipal de Abastecimiento y Saneamiento de Granada, S.A.</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Mejora de las infraestructuras y resiliencia hídrica en el ciclo integral del agua en la Avenida Don Bosco, entre la Avenida de Cádiz y la Avenida Fernando de los Ríos (Granada).</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Obra 2025-00017_3</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="M53" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>E*-4</t>
+        </is>
+      </c>
+      <c r="O53" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>Oferta económica 60 | Oferta técnica 40 (JV)</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="n"/>
+      <c r="R53" s="2" t="n"/>
+      <c r="S53" s="4" t="n"/>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>45232150</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>PCAP</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>PPT</t>
+        </is>
+      </c>
+      <c r="W53" s="8" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+      <c r="X53" s="9" t="n">
+        <v>46310</v>
+      </c>
+      <c r="Y53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="3" t="n">
+        <v>46350.45833333334</v>
+      </c>
+      <c r="C54" s="4">
+        <f>IF(B54="","",INT(B54)-TODAY())</f>
+        <v/>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>3246355.87</v>
+      </c>
+      <c r="E54" s="5" t="n">
+        <v>3246355.87</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Comisión Ejecutiva de la Gerencia de Urbanismo de Sevilla</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Obras del Proyecto básico y de ejecución para rehabilitación, consolidación y puesta en valor de la sala de Profundis y las viviendas anexas del Real Monasterio de Santa Clara.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>19/2026</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Abierto</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>K7-4</t>
+        </is>
+      </c>
+      <c r="O54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>1. OFERTA ECONÓMICA 20 | 2. MAYOR CUALIFICACIÓN Y EXPERIENCIA DEL EQUIPO TÉCNICO. SUBCRITERIO D. BAREMACIÓN DEL PERFIL 4 RESTAURADOR. 10 | 3. AMPLIACIÓN DEL PLAZO DE GARANTÍA. 30 | 2. MAYOR CUALIFICACIÓN Y EXPERIENCIA DEL EQUIPO TÉCNICO. SUBCRITERIO B. BAREMACIÓN DEL PERFIL 2. ENCARGADO. 15 | 2. MAYOR CUALIFICACIÓN Y EXPERIENCIA DEL EQUIPO TÉCNICO. SUBCRITERIO C. BAREMACIÓN DEL PERFIL 3. TÉCNICO EN PREVENCIÓN DE RIESGOS LABORALES. 10 | 2. MAYOR CUALIFICACIÓN Y EXPERIENCIA DEL EQUIPO TÉCNICO. SUBCRITERIO A. BAREMACIÓN DEL PERFIL 1. TÉCNICO JEFE DE OBRA. 15</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>definitiva 5%; complementaria 5%</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>FÓRMULA 831. Obras de restauración de edificios.</t>
+        </is>
+      </c>
+      <c r="S54" s="4" t="n"/>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>45212300</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>PCAP</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="n"/>
+      <c r="W54" s="8" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+      <c r="X54" s="9" t="n">
+        <v>46310</v>
+      </c>
+      <c r="Y54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="3" t="n">
+        <v>48099.58333333334</v>
+      </c>
+      <c r="C55" s="4">
+        <f>IF(B55="","",INT(B55)-TODAY())</f>
+        <v/>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Andalucía</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Consejo de Administración de la Empresa Municipal de Aguas de Córdoba, S.A. (EMACSA)</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Sistema dinámico de adquisición de obras en redes e instalaciones para la Empresa Municipal de Aguas de Córdoba, S.A.</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>SDA32/2026</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Restringido</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="n"/>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
           <t>[lote 1] | Price 100</t>
         </is>
       </c>
-      <c r="Q50" s="2" t="n"/>
-      <c r="R50" s="2" t="n"/>
-      <c r="S50" s="4" t="n">
+      <c r="Q55" s="2" t="n"/>
+      <c r="R55" s="2" t="n"/>
+      <c r="S55" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="T50" s="2" t="inlineStr">
+      <c r="T55" s="2" t="inlineStr">
         <is>
           <t>45231110; 45232152; 45252100; 45231300; 45232423; 45232411; 45252120; 45232150; 45232400; 45232410; 45232151</t>
         </is>
       </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>PCAP</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>PCAP</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
         <is>
           <t>PPT</t>
         </is>
       </c>
-      <c r="W50" s="8" t="inlineStr">
-        <is>
-          <t>Ver</t>
-        </is>
-      </c>
-      <c r="X50" s="9" t="n">
-        <v>46310</v>
-      </c>
-      <c r="Y50" s="2" t="n"/>
+      <c r="W55" s="8" t="inlineStr">
+        <is>
+          <t>Ver</t>
+        </is>
+      </c>
+      <c r="X55" s="9" t="n">
+        <v>46310</v>
+      </c>
+      <c r="Y55" s="2" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:C50">
+  <conditionalFormatting sqref="C2:C55">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>AND(ISNUMBER(C2),C2&lt;=7)</formula>
     </cfRule>
@@ -5346,12 +5822,12 @@
       <formula>AND(ISNUMBER(C2),C2&lt;=14)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A50">
+  <conditionalFormatting sqref="A2:A55">
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>A2="SÍ"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y50">
+  <conditionalFormatting sqref="Y2:Y55">
     <cfRule type="expression" priority="4" dxfId="3">
       <formula>LEN(Y2)&gt;0</formula>
     </cfRule>
@@ -5376,42 +5852,42 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V7" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U8" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V8" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V11" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V13" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U14" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V14" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W14" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V15" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W15" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V16" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W16" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V17" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W17" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V18" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W18" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V19" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W19" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U9" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U10" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V10" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U11" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V11" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U12" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V12" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U13" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V13" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U14" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V14" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W14" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U15" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V15" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W15" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U16" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V16" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W16" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U17" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V17" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W17" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U18" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V18" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W18" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U19" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V19" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W19" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U20" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V20" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U21" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V21" r:id="rId58"/>
@@ -5420,93 +5896,107 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V22" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W22" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U23" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V23" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W23" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U24" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V24" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W24" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U25" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V25" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W25" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U26" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V26" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W26" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U27" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V27" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U28" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V28" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W28" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U29" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V29" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U30" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V30" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W30" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U31" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V31" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W31" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U32" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V32" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W32" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V33" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W33" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U34" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V34" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W34" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U35" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V35" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W35" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U36" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V36" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W36" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U37" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V37" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W37" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U38" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V38" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W38" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U39" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V39" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W39" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U40" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V40" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W40" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U41" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V41" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W41" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U42" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V42" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W42" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U43" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V43" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W43" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U44" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V44" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W44" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U45" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V45" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W45" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U46" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V46" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W46" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U47" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V47" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W47" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U48" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V48" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W48" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U49" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W23" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U24" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V24" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W24" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U25" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V25" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W25" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U26" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V26" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W26" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U27" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V27" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U28" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V28" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W28" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U29" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V29" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U30" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V30" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W30" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U31" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V31" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W31" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U32" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V32" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W32" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U33" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V33" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W33" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U34" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V34" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W34" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U35" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V35" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W35" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U36" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V36" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W36" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U37" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V37" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W37" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U38" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V38" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W38" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U39" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V39" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W39" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U40" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V40" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W40" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U41" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V41" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W41" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U42" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V42" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W42" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U43" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V43" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W43" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U44" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V44" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W44" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U45" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V45" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W45" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U46" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V46" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W46" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U47" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V47" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W47" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U48" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V48" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W48" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U49" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V49" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W49" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U50" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V50" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W50" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U51" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V51" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W51" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U52" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V52" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W52" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U53" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V53" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W53" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U54" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W54" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="U55" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V55" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W55" r:id="rId159"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId146"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId160"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5517,7 +6007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5542,7 +6032,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46310.50722222222</v>
+        <v>46310.53538194444</v>
       </c>
     </row>
     <row r="4">
@@ -5565,7 +6055,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>entre 500.000,00 € y 10.000.000,00 €</t>
+          <t>entre 500.000,00 € y ∞</t>
         </is>
       </c>
     </row>
@@ -5620,7 +6110,7 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>COUNTA('En plazo'!$J$2:$J$50)</f>
+        <f>COUNTA('En plazo'!$J$2:$J$55)</f>
         <v/>
       </c>
     </row>
@@ -5631,7 +6121,7 @@
         </is>
       </c>
       <c r="B11" s="15">
-        <f>SUM('En plazo'!$D$2:$D$50)</f>
+        <f>SUM('En plazo'!$D$2:$D$55)</f>
         <v/>
       </c>
     </row>
@@ -5642,7 +6132,7 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>COUNTIF('En plazo'!$A$2:$A$50,"SÍ")</f>
+        <f>COUNTIF('En plazo'!$A$2:$A$55,"SÍ")</f>
         <v/>
       </c>
     </row>
@@ -5653,7 +6143,7 @@
         </is>
       </c>
       <c r="B13" s="14">
-        <f>COUNTIF('En plazo'!$Y$2:$Y$50,"?*")</f>
+        <f>COUNTIF('En plazo'!$Y$2:$Y$55,"?*")</f>
         <v/>
       </c>
     </row>
@@ -5664,7 +6154,7 @@
         </is>
       </c>
       <c r="B14" s="14">
-        <f>COUNTIFS('En plazo'!$C$2:$C$50,"&gt;=0",'En plazo'!$C$2:$C$50,"&lt;=7")</f>
+        <f>COUNTIFS('En plazo'!$C$2:$C$55,"&gt;=0",'En plazo'!$C$2:$C$55,"&lt;=7")</f>
         <v/>
       </c>
     </row>
@@ -5719,19 +6209,19 @@
         </is>
       </c>
       <c r="C18" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>SUMIFS('En plazo'!$D$2:$D$50,'En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"")</f>
+        <f>SUMIFS('En plazo'!$D$2:$D$55,'En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"")</f>
         <v/>
       </c>
       <c r="E18" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"",'En plazo'!$A$2:$A$50,"SÍ")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"",'En plazo'!$A$2:$A$55,"SÍ")</f>
         <v/>
       </c>
       <c r="F18" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"",'En plazo'!$C$2:$C$50,"&gt;=0",'En plazo'!$C$2:$C$50,"&lt;=7")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"",'En plazo'!$C$2:$C$55,"&gt;=0",'En plazo'!$C$2:$C$55,"&lt;=7")</f>
         <v/>
       </c>
     </row>
@@ -5747,19 +6237,19 @@
         </is>
       </c>
       <c r="C19" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Almería")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Almería")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>SUMIFS('En plazo'!$D$2:$D$50,'En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Almería")</f>
+        <f>SUMIFS('En plazo'!$D$2:$D$55,'En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Almería")</f>
         <v/>
       </c>
       <c r="E19" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Almería",'En plazo'!$A$2:$A$50,"SÍ")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Almería",'En plazo'!$A$2:$A$55,"SÍ")</f>
         <v/>
       </c>
       <c r="F19" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Almería",'En plazo'!$C$2:$C$50,"&gt;=0",'En plazo'!$C$2:$C$50,"&lt;=7")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Almería",'En plazo'!$C$2:$C$55,"&gt;=0",'En plazo'!$C$2:$C$55,"&lt;=7")</f>
         <v/>
       </c>
     </row>
@@ -5775,19 +6265,19 @@
         </is>
       </c>
       <c r="C20" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Cádiz")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Cádiz")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>SUMIFS('En plazo'!$D$2:$D$50,'En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Cádiz")</f>
+        <f>SUMIFS('En plazo'!$D$2:$D$55,'En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Cádiz")</f>
         <v/>
       </c>
       <c r="E20" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Cádiz",'En plazo'!$A$2:$A$50,"SÍ")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Cádiz",'En plazo'!$A$2:$A$55,"SÍ")</f>
         <v/>
       </c>
       <c r="F20" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Cádiz",'En plazo'!$C$2:$C$50,"&gt;=0",'En plazo'!$C$2:$C$50,"&lt;=7")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Cádiz",'En plazo'!$C$2:$C$55,"&gt;=0",'En plazo'!$C$2:$C$55,"&lt;=7")</f>
         <v/>
       </c>
     </row>
@@ -5803,19 +6293,19 @@
         </is>
       </c>
       <c r="C21" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Córdoba")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Córdoba")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>SUMIFS('En plazo'!$D$2:$D$50,'En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Córdoba")</f>
+        <f>SUMIFS('En plazo'!$D$2:$D$55,'En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Córdoba")</f>
         <v/>
       </c>
       <c r="E21" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Córdoba",'En plazo'!$A$2:$A$50,"SÍ")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Córdoba",'En plazo'!$A$2:$A$55,"SÍ")</f>
         <v/>
       </c>
       <c r="F21" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Córdoba",'En plazo'!$C$2:$C$50,"&gt;=0",'En plazo'!$C$2:$C$50,"&lt;=7")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Córdoba",'En plazo'!$C$2:$C$55,"&gt;=0",'En plazo'!$C$2:$C$55,"&lt;=7")</f>
         <v/>
       </c>
     </row>
@@ -5831,19 +6321,19 @@
         </is>
       </c>
       <c r="C22" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Granada")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Granada")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>SUMIFS('En plazo'!$D$2:$D$50,'En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Granada")</f>
+        <f>SUMIFS('En plazo'!$D$2:$D$55,'En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Granada")</f>
         <v/>
       </c>
       <c r="E22" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Granada",'En plazo'!$A$2:$A$50,"SÍ")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Granada",'En plazo'!$A$2:$A$55,"SÍ")</f>
         <v/>
       </c>
       <c r="F22" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Granada",'En plazo'!$C$2:$C$50,"&gt;=0",'En plazo'!$C$2:$C$50,"&lt;=7")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Granada",'En plazo'!$C$2:$C$55,"&gt;=0",'En plazo'!$C$2:$C$55,"&lt;=7")</f>
         <v/>
       </c>
     </row>
@@ -5859,19 +6349,19 @@
         </is>
       </c>
       <c r="C23" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Huelva")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Huelva")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>SUMIFS('En plazo'!$D$2:$D$50,'En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Huelva")</f>
+        <f>SUMIFS('En plazo'!$D$2:$D$55,'En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Huelva")</f>
         <v/>
       </c>
       <c r="E23" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Huelva",'En plazo'!$A$2:$A$50,"SÍ")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Huelva",'En plazo'!$A$2:$A$55,"SÍ")</f>
         <v/>
       </c>
       <c r="F23" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Huelva",'En plazo'!$C$2:$C$50,"&gt;=0",'En plazo'!$C$2:$C$50,"&lt;=7")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Huelva",'En plazo'!$C$2:$C$55,"&gt;=0",'En plazo'!$C$2:$C$55,"&lt;=7")</f>
         <v/>
       </c>
     </row>
@@ -5883,23 +6373,23 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Málaga</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="C24" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Málaga")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Jaén")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>SUMIFS('En plazo'!$D$2:$D$50,'En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Málaga")</f>
+        <f>SUMIFS('En plazo'!$D$2:$D$55,'En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Jaén")</f>
         <v/>
       </c>
       <c r="E24" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Málaga",'En plazo'!$A$2:$A$50,"SÍ")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Jaén",'En plazo'!$A$2:$A$55,"SÍ")</f>
         <v/>
       </c>
       <c r="F24" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Málaga",'En plazo'!$C$2:$C$50,"&gt;=0",'En plazo'!$C$2:$C$50,"&lt;=7")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Jaén",'En plazo'!$C$2:$C$55,"&gt;=0",'En plazo'!$C$2:$C$55,"&lt;=7")</f>
         <v/>
       </c>
     </row>
@@ -5911,51 +6401,51 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="C25" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Sevilla")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Málaga")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>SUMIFS('En plazo'!$D$2:$D$50,'En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Sevilla")</f>
+        <f>SUMIFS('En plazo'!$D$2:$D$55,'En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Málaga")</f>
         <v/>
       </c>
       <c r="E25" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Sevilla",'En plazo'!$A$2:$A$50,"SÍ")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Málaga",'En plazo'!$A$2:$A$55,"SÍ")</f>
         <v/>
       </c>
       <c r="F25" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Andalucía",'En plazo'!$G$2:$G$50,"Sevilla",'En plazo'!$C$2:$C$50,"&gt;=0",'En plazo'!$C$2:$C$50,"&lt;=7")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Málaga",'En plazo'!$C$2:$C$55,"&gt;=0",'En plazo'!$C$2:$C$55,"&lt;=7")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>(sin provincia)</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="C26" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Comunitat Valenciana",'En plazo'!$G$2:$G$50,"")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Sevilla")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>SUMIFS('En plazo'!$D$2:$D$50,'En plazo'!$F$2:$F$50,"Comunitat Valenciana",'En plazo'!$G$2:$G$50,"")</f>
+        <f>SUMIFS('En plazo'!$D$2:$D$55,'En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Sevilla")</f>
         <v/>
       </c>
       <c r="E26" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Comunitat Valenciana",'En plazo'!$G$2:$G$50,"",'En plazo'!$A$2:$A$50,"SÍ")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Sevilla",'En plazo'!$A$2:$A$55,"SÍ")</f>
         <v/>
       </c>
       <c r="F26" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Comunitat Valenciana",'En plazo'!$G$2:$G$50,"",'En plazo'!$C$2:$C$50,"&gt;=0",'En plazo'!$C$2:$C$50,"&lt;=7")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Andalucía",'En plazo'!$G$2:$G$55,"Sevilla",'En plazo'!$C$2:$C$55,"&gt;=0",'En plazo'!$C$2:$C$55,"&lt;=7")</f>
         <v/>
       </c>
     </row>
@@ -5967,23 +6457,23 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Alicante</t>
+          <t>(sin provincia)</t>
         </is>
       </c>
       <c r="C27" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Comunitat Valenciana",'En plazo'!$G$2:$G$50,"Alicante")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>SUMIFS('En plazo'!$D$2:$D$50,'En plazo'!$F$2:$F$50,"Comunitat Valenciana",'En plazo'!$G$2:$G$50,"Alicante")</f>
+        <f>SUMIFS('En plazo'!$D$2:$D$55,'En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"")</f>
         <v/>
       </c>
       <c r="E27" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Comunitat Valenciana",'En plazo'!$G$2:$G$50,"Alicante",'En plazo'!$A$2:$A$50,"SÍ")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"",'En plazo'!$A$2:$A$55,"SÍ")</f>
         <v/>
       </c>
       <c r="F27" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Comunitat Valenciana",'En plazo'!$G$2:$G$50,"Alicante",'En plazo'!$C$2:$C$50,"&gt;=0",'En plazo'!$C$2:$C$50,"&lt;=7")</f>
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"",'En plazo'!$C$2:$C$55,"&gt;=0",'En plazo'!$C$2:$C$55,"&lt;=7")</f>
         <v/>
       </c>
     </row>
@@ -5995,72 +6485,128 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
+          <t>Alicante</t>
+        </is>
+      </c>
+      <c r="C28" s="18">
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"Alicante")</f>
+        <v/>
+      </c>
+      <c r="D28" s="5">
+        <f>SUMIFS('En plazo'!$D$2:$D$55,'En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"Alicante")</f>
+        <v/>
+      </c>
+      <c r="E28" s="18">
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"Alicante",'En plazo'!$A$2:$A$55,"SÍ")</f>
+        <v/>
+      </c>
+      <c r="F28" s="18">
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"Alicante",'En plazo'!$C$2:$C$55,"&gt;=0",'En plazo'!$C$2:$C$55,"&lt;=7")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Comunitat Valenciana</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="C29" s="18">
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"Castellón")</f>
+        <v/>
+      </c>
+      <c r="D29" s="5">
+        <f>SUMIFS('En plazo'!$D$2:$D$55,'En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"Castellón")</f>
+        <v/>
+      </c>
+      <c r="E29" s="18">
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"Castellón",'En plazo'!$A$2:$A$55,"SÍ")</f>
+        <v/>
+      </c>
+      <c r="F29" s="18">
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"Castellón",'En plazo'!$C$2:$C$55,"&gt;=0",'En plazo'!$C$2:$C$55,"&lt;=7")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Comunitat Valenciana</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="C28" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Comunitat Valenciana",'En plazo'!$G$2:$G$50,"Valencia")</f>
+      <c r="C30" s="18">
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"Valencia")</f>
         <v/>
       </c>
-      <c r="D28" s="5">
-        <f>SUMIFS('En plazo'!$D$2:$D$50,'En plazo'!$F$2:$F$50,"Comunitat Valenciana",'En plazo'!$G$2:$G$50,"Valencia")</f>
+      <c r="D30" s="5">
+        <f>SUMIFS('En plazo'!$D$2:$D$55,'En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"Valencia")</f>
         <v/>
       </c>
-      <c r="E28" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Comunitat Valenciana",'En plazo'!$G$2:$G$50,"Valencia",'En plazo'!$A$2:$A$50,"SÍ")</f>
+      <c r="E30" s="18">
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"Valencia",'En plazo'!$A$2:$A$55,"SÍ")</f>
         <v/>
       </c>
-      <c r="F28" s="18">
-        <f>COUNTIFS('En plazo'!$F$2:$F$50,"Comunitat Valenciana",'En plazo'!$G$2:$G$50,"Valencia",'En plazo'!$C$2:$C$50,"&gt;=0",'En plazo'!$C$2:$C$50,"&lt;=7")</f>
+      <c r="F30" s="18">
+        <f>COUNTIFS('En plazo'!$F$2:$F$55,"Comunitat Valenciana",'En plazo'!$G$2:$G$55,"Valencia",'En plazo'!$C$2:$C$55,"&gt;=0",'En plazo'!$C$2:$C$55,"&lt;=7")</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C29" s="19">
-        <f>SUM(C18:C28)</f>
+      <c r="C31" s="19">
+        <f>SUM(C18:C30)</f>
         <v/>
       </c>
-      <c r="D29" s="20">
-        <f>SUM(D18:D28)</f>
+      <c r="D31" s="20">
+        <f>SUM(D18:D30)</f>
         <v/>
       </c>
-      <c r="E29" s="19">
-        <f>SUM(E18:E28)</f>
+      <c r="E31" s="19">
+        <f>SUM(E18:E30)</f>
         <v/>
       </c>
-      <c r="F29" s="19">
-        <f>SUM(F18:F28)</f>
+      <c r="F31" s="19">
+        <f>SUM(F18:F30)</f>
         <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="21" t="inlineStr">
-        <is>
-          <t>Fuente: Plataforma de Contratación del Sector Público (feed ATOM licitacionesPerfilesContratanteCompleto3) y ficheros mensuales de datos abiertos del Ministerio de Hacienda.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="21" t="inlineStr">
-        <is>
-          <t>Los días restantes y los vencimientos se recalculan con la fecha del día al abrir el libro.</t>
-        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="21" t="inlineStr">
         <is>
-          <t>Plazo de ejecución en meses: los plazos en días se dividen entre 30 y los de años se multiplican por 12.</t>
+          <t>Fuente: Plataforma de Contratación del Sector Público (feed ATOM licitacionesPerfilesContratanteCompleto3) y ficheros mensuales de datos abiertos del Ministerio de Hacienda.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Los días restantes y los vencimientos se recalculan con la fecha del día al abrir el libro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Plazo de ejecución en meses: los plazos en días se dividen entre 30 y los de años se multiplican por 12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>Este libro se regenera en cada ejecución: las anotaciones que se hagan en él se pierden. Para el seguimiento, copiar las filas al libro de preselección.</t>
         </is>
